--- a/examples/sentetik_ornek/sonuclar.xlsx
+++ b/examples/sentetik_ornek/sonuclar.xlsx
@@ -456,7 +456,7 @@
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="18" customWidth="1" min="12" max="12"/>
     <col width="26" customWidth="1" min="13" max="13"/>
-    <col width="44" customWidth="1" min="14" max="14"/>
+    <col width="39" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -663,7 +663,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>LAC &lt; 3 sigma: HVL/TVL/MFP guvenilir degil</t>
+          <t>LAC &lt; 3σ: HVL/TVL/MFP güvenilir değil</t>
         </is>
       </c>
     </row>
@@ -733,7 +733,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>LAC &lt; 3 sigma: HVL/TVL/MFP guvenilir degil</t>
+          <t>LAC &lt; 3σ: HVL/TVL/MFP güvenilir değil</t>
         </is>
       </c>
     </row>
@@ -869,7 +869,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>LAC &lt; 3 sigma: HVL/TVL/MFP guvenilir degil</t>
+          <t>LAC &lt; 3σ: HVL/TVL/MFP güvenilir değil</t>
         </is>
       </c>
     </row>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>LAC &lt; 3 sigma: HVL/TVL/MFP guvenilir degil</t>
+          <t>LAC &lt; 3σ: HVL/TVL/MFP güvenilir değil</t>
         </is>
       </c>
     </row>
@@ -1207,7 +1207,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>LAC &lt; 3 sigma: HVL/TVL/MFP guvenilir degil</t>
+          <t>LAC &lt; 3σ: HVL/TVL/MFP güvenilir değil</t>
         </is>
       </c>
     </row>
@@ -1377,7 +1377,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Spektrumlarda tespit edilemeyen cizgiler (analiz disi birakildi): Am-241 59.5 (en yuksek 0.8 sigma); Co-57 122 (en yuksek 2.5 sigma)</t>
+          <t>Spektrumlarda tespit edilemeyen çizgiler (analiz dışı bırakıldı): Am-241 59.5 (en yüksek 0.8σ); Co-57 122 (en yüksek 2.5σ)</t>
         </is>
       </c>
     </row>
@@ -1607,13 +1607,13 @@
     <col width="20" customWidth="1" min="48" max="48"/>
     <col width="20" customWidth="1" min="49" max="49"/>
     <col width="21" customWidth="1" min="50" max="50"/>
-    <col width="22" customWidth="1" min="51" max="51"/>
+    <col width="21" customWidth="1" min="51" max="51"/>
     <col width="21" customWidth="1" min="52" max="52"/>
     <col width="20" customWidth="1" min="53" max="53"/>
     <col width="24" customWidth="1" min="54" max="54"/>
     <col width="21" customWidth="1" min="55" max="55"/>
     <col width="20" customWidth="1" min="56" max="56"/>
-    <col width="44" customWidth="1" min="57" max="57"/>
+    <col width="39" customWidth="1" min="57" max="57"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1968,13 +1968,13 @@
         <v>14.27473646102501</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>5.154008617644307</v>
+        <v>5.154009202964633</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>2.016666460271793</v>
+        <v>2.016666231247005</v>
       </c>
       <c r="V2" s="2" t="n">
-        <v>0.1412752148369249</v>
+        <v>0.1412751987928607</v>
       </c>
       <c r="W2" s="2" t="n">
         <v>0.2</v>
@@ -2034,22 +2034,22 @@
         <v>0.05735188883641247</v>
       </c>
       <c r="AP2" s="2" t="n">
-        <v>33.55516001704655</v>
+        <v>33.55515585102087</v>
       </c>
       <c r="AQ2" s="2" t="n">
-        <v>2.358833309808101</v>
+        <v>2.358833016948221</v>
       </c>
       <c r="AR2" s="3" t="n">
-        <v>3.802158477058641e+23</v>
+        <v>3.80215800500338e+23</v>
       </c>
       <c r="AS2" s="3" t="n">
-        <v>2.672810399443467e+22</v>
+        <v>2.672810067601905e+22</v>
       </c>
       <c r="AT2" s="3" t="n">
-        <v>2.421974949886355e+24</v>
+        <v>2.421974649187153e+24</v>
       </c>
       <c r="AU2" s="3" t="n">
-        <v>1.702721733277541e+23</v>
+        <v>1.702721521876897e+23</v>
       </c>
       <c r="AV2" s="2" t="n">
         <v>72.00105954340778</v>
@@ -2058,25 +2058,25 @@
         <v>5.061471842368986</v>
       </c>
       <c r="AX2" s="2" t="n">
-        <v>2.145752233243117</v>
+        <v>2.145752499648045</v>
       </c>
       <c r="AY2" s="2" t="n">
-        <v>0.8091065333821519</v>
+        <v>0.8091066252691731</v>
       </c>
       <c r="AZ2" s="2" t="n">
-        <v>0.1344870045787303</v>
+        <v>0.1344869893055761</v>
       </c>
       <c r="BA2" s="2" t="n">
-        <v>33.27784805081173</v>
+        <v>33.2778476984484</v>
       </c>
       <c r="BB2" s="3" t="n">
-        <v>3.770736065641922e+23</v>
+        <v>3.770736025715389e+23</v>
       </c>
       <c r="BC2" s="2" t="n">
-        <v>0.8333230135896473</v>
+        <v>0.8333115623502168</v>
       </c>
       <c r="BD2" s="2" t="n">
-        <v>7.088298817298562</v>
+        <v>7.08829801230866</v>
       </c>
       <c r="BE2" t="inlineStr"/>
     </row>
@@ -2145,13 +2145,13 @@
         <v>1.343018729574148</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>0.9312119431632206</v>
+        <v>0.9312121114180388</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>1.494955678206653</v>
+        <v>1.49495540809258</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>1.113130923111312</v>
+        <v>1.113130721986736</v>
       </c>
       <c r="W3" s="2" t="n">
         <v>0.2</v>
@@ -2211,22 +2211,22 @@
         <v>0.08136520707143691</v>
       </c>
       <c r="AP3" s="2" t="n">
-        <v>22.53191455512147</v>
+        <v>22.53191120265777</v>
       </c>
       <c r="AQ3" s="2" t="n">
-        <v>16.77758328145946</v>
+        <v>16.77758078516743</v>
       </c>
       <c r="AR3" s="3" t="n">
-        <v>2.553106880926642e+23</v>
+        <v>2.553106501056654e+23</v>
       </c>
       <c r="AS3" s="3" t="n">
-        <v>1.901079609387993e+23</v>
+        <v>1.90107932653141e+23</v>
       </c>
       <c r="AT3" s="3" t="n">
-        <v>1.626329083150271e+24</v>
+        <v>1.626328841173089e+24</v>
       </c>
       <c r="AU3" s="3" t="n">
-        <v>1.210988608292521e+24</v>
+        <v>1.210988428112744e+24</v>
       </c>
       <c r="AV3" s="2" t="n">
         <v>9.643540882980556</v>
@@ -2235,29 +2235,29 @@
         <v>7.180717372975728</v>
       </c>
       <c r="AX3" s="2" t="n">
-        <v>0.4279947387244372</v>
+        <v>0.4279948024046465</v>
       </c>
       <c r="AY3" s="2" t="n">
-        <v>0.1461871182359844</v>
+        <v>0.1461871446496136</v>
       </c>
       <c r="AZ3" s="2" t="n">
-        <v>0.7443495389517917</v>
+        <v>0.7443494044599881</v>
       </c>
       <c r="BA3" s="2" t="n">
-        <v>30.14392317255951</v>
+        <v>30.14392413404001</v>
       </c>
       <c r="BB3" s="3" t="n">
-        <v>3.415628861973148e+23</v>
+        <v>3.415628970919171e+23</v>
       </c>
       <c r="BC3" s="2" t="n">
-        <v>-25.25221608966737</v>
+        <v>-25.25222959537099</v>
       </c>
       <c r="BD3" s="2" t="n">
-        <v>55.65826049056668</v>
+        <v>55.65825043402813</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>LAC &lt; 3 sigma: HVL/TVL/MFP guvenilir degil</t>
+          <t>LAC &lt; 3σ: HVL/TVL/MFP güvenilir değil</t>
         </is>
       </c>
     </row>
@@ -2326,13 +2326,13 @@
         <v>2.965581864565676</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>0.7726659251229667</v>
+        <v>0.7726660408861314</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>1.586994876839577</v>
+        <v>1.586994639071201</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>0.5351377737373639</v>
+        <v>0.5351376935614031</v>
       </c>
       <c r="W4" s="2" t="n">
         <v>0.2</v>
@@ -2392,22 +2392,22 @@
         <v>0.03246034689448935</v>
       </c>
       <c r="AP4" s="2" t="n">
-        <v>22.69404816833188</v>
+        <v>22.69404562087823</v>
       </c>
       <c r="AQ4" s="2" t="n">
-        <v>7.653626631941197</v>
+        <v>7.653625772805842</v>
       </c>
       <c r="AR4" s="3" t="n">
-        <v>2.571478353200085e+23</v>
+        <v>2.571478064546343e+23</v>
       </c>
       <c r="AS4" s="3" t="n">
-        <v>8.672377471629875e+22</v>
+        <v>8.672376498137641e+22</v>
       </c>
       <c r="AT4" s="3" t="n">
-        <v>1.638031710988454e+24</v>
+        <v>1.638031527116021e+24</v>
       </c>
       <c r="AU4" s="3" t="n">
-        <v>5.524324399116141e+23</v>
+        <v>5.524323778999349e+23</v>
       </c>
       <c r="AV4" s="2" t="n">
         <v>8.494287505290718</v>
@@ -2416,29 +2416,29 @@
         <v>2.864720502381708</v>
       </c>
       <c r="AX4" s="2" t="n">
-        <v>0.3742958260370648</v>
+        <v>0.3742958680525469</v>
       </c>
       <c r="AY4" s="2" t="n">
-        <v>0.1212976334572946</v>
+        <v>0.1212976516304759</v>
       </c>
       <c r="AZ4" s="2" t="n">
-        <v>0.8970852188798589</v>
+        <v>0.8970850844758363</v>
       </c>
       <c r="BA4" s="2" t="n">
-        <v>28.60002700642107</v>
+        <v>28.60002808095189</v>
       </c>
       <c r="BB4" s="3" t="n">
-        <v>3.240688915544655e+23</v>
+        <v>3.240689037300489e+23</v>
       </c>
       <c r="BC4" s="2" t="n">
-        <v>-20.65025615802118</v>
+        <v>-20.65026804643995</v>
       </c>
       <c r="BD4" s="2" t="n">
-        <v>26.76090700971318</v>
+        <v>26.7609030003131</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>LAC &lt; 3 sigma: HVL/TVL/MFP guvenilir degil</t>
+          <t>LAC &lt; 3σ: HVL/TVL/MFP güvenilir değil</t>
         </is>
       </c>
     </row>
@@ -2507,13 +2507,13 @@
         <v>3.08952723080917</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>0.5046963530564196</v>
+        <v>0.5046963885603317</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>2.098043986084978</v>
+        <v>2.098043838493731</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>0.6790825357235919</v>
+        <v>0.6790824879521252</v>
       </c>
       <c r="W5" s="2" t="n">
         <v>0.2</v>
@@ -2573,22 +2573,22 @@
         <v>0.02690630628662187</v>
       </c>
       <c r="AP5" s="2" t="n">
-        <v>27.48048356101584</v>
+        <v>27.48048213288326</v>
       </c>
       <c r="AQ5" s="2" t="n">
-        <v>8.896171048733246</v>
+        <v>8.896170586408347</v>
       </c>
       <c r="AR5" s="3" t="n">
-        <v>3.113832670507515e+23</v>
+        <v>3.11383250868482e+23</v>
       </c>
       <c r="AS5" s="3" t="n">
-        <v>1.00803131766087e+23</v>
+        <v>1.008031265274515e+23</v>
       </c>
       <c r="AT5" s="3" t="n">
-        <v>1.983511411113287e+24</v>
+        <v>1.983511308032231e+24</v>
       </c>
       <c r="AU5" s="3" t="n">
-        <v>6.421184660125047e+23</v>
+        <v>6.421184326422654e+23</v>
       </c>
       <c r="AV5" s="2" t="n">
         <v>7.33507277643852</v>
@@ -2597,25 +2597,25 @@
         <v>2.374560183019267</v>
       </c>
       <c r="AX5" s="2" t="n">
-        <v>0.2669193487862835</v>
+        <v>0.2669193626578095</v>
       </c>
       <c r="AY5" s="2" t="n">
-        <v>0.07923019671215378</v>
+        <v>0.07923020228576637</v>
       </c>
       <c r="AZ5" s="2" t="n">
-        <v>1.373394470481658</v>
+        <v>1.373394373867381</v>
       </c>
       <c r="BA5" s="2" t="n">
-        <v>26.19628925158559</v>
+        <v>26.19628973302349</v>
       </c>
       <c r="BB5" s="3" t="n">
-        <v>2.968319721759537e+23</v>
+        <v>2.9683197763116e+23</v>
       </c>
       <c r="BC5" s="2" t="n">
-        <v>4.902199304248881</v>
+        <v>4.902191924686525</v>
       </c>
       <c r="BD5" s="2" t="n">
-        <v>33.95966109281979</v>
+        <v>33.95965870385714</v>
       </c>
       <c r="BE5" t="inlineStr"/>
     </row>
@@ -2684,13 +2684,13 @@
         <v>2.283321960425025</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>0.3649451288823548</v>
+        <v>0.3649451484627882</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>1.951217719221146</v>
+        <v>1.951217614532294</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>0.8545521626122056</v>
+        <v>0.8545521167628449</v>
       </c>
       <c r="W6" s="2" t="n">
         <v>0.2</v>
@@ -2750,22 +2750,22 @@
         <v>0.02448135121418641</v>
       </c>
       <c r="AP6" s="2" t="n">
-        <v>24.85613971635959</v>
+        <v>24.85613882669739</v>
       </c>
       <c r="AQ6" s="2" t="n">
-        <v>10.88692400473625</v>
+        <v>10.88692361506654</v>
       </c>
       <c r="AR6" s="3" t="n">
-        <v>2.816466447529965e+23</v>
+        <v>2.816466346721723e+23</v>
       </c>
       <c r="AS6" s="3" t="n">
-        <v>1.233604917177341e+23</v>
+        <v>1.233604873023596e+23</v>
       </c>
       <c r="AT6" s="3" t="n">
-        <v>1.794089127076588e+24</v>
+        <v>1.794089062861738e+24</v>
       </c>
       <c r="AU6" s="3" t="n">
-        <v>7.858080146910282e+23</v>
+        <v>7.85807986565032e+23</v>
       </c>
       <c r="AV6" s="2" t="n">
         <v>4.93279394198141</v>
@@ -2774,29 +2774,29 @@
         <v>2.160550809184148</v>
       </c>
       <c r="AX6" s="2" t="n">
-        <v>0.1984537421446335</v>
+        <v>0.1984537492477799</v>
       </c>
       <c r="AY6" s="2" t="n">
-        <v>0.05729122902391755</v>
+        <v>0.05729123209776895</v>
       </c>
       <c r="AZ6" s="2" t="n">
-        <v>1.899318899481437</v>
+        <v>1.899318797577117</v>
       </c>
       <c r="BA6" s="2" t="n">
-        <v>25.47756662058322</v>
+        <v>25.47756707562872</v>
       </c>
       <c r="BB6" s="3" t="n">
-        <v>2.886880761470529e+23</v>
+        <v>2.88688081303205e+23</v>
       </c>
       <c r="BC6" s="2" t="n">
-        <v>-2.439114038942717</v>
+        <v>-2.439119273385309</v>
       </c>
       <c r="BD6" s="2" t="n">
-        <v>42.73141217474336</v>
+        <v>42.73140988207123</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>LAC &lt; 3 sigma: HVL/TVL/MFP guvenilir degil</t>
+          <t>LAC &lt; 3σ: HVL/TVL/MFP güvenilir değil</t>
         </is>
       </c>
     </row>
@@ -2865,13 +2865,13 @@
         <v>4.506011387696815</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>0.3411182000345155</v>
+        <v>0.341118237048898</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>2.005247058533038</v>
+        <v>2.005246840945781</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>0.4450159766591252</v>
+        <v>0.4450159283709078</v>
       </c>
       <c r="W7" s="2" t="n">
         <v>0.2</v>
@@ -2931,22 +2931,22 @@
         <v>0.01191959782795906</v>
       </c>
       <c r="AP7" s="2" t="n">
-        <v>25.48483186394954</v>
+        <v>25.48482990062792</v>
       </c>
       <c r="AQ7" s="2" t="n">
-        <v>5.657701413243935</v>
+        <v>5.657700977381238</v>
       </c>
       <c r="AR7" s="3" t="n">
-        <v>2.887703991240232e+23</v>
+        <v>2.887703768774895e+23</v>
       </c>
       <c r="AS7" s="3" t="n">
-        <v>6.410780749698084e+22</v>
+        <v>6.410780255819037e+22</v>
       </c>
       <c r="AT7" s="3" t="n">
-        <v>1.839467442420028e+24</v>
+        <v>1.839467300709608e+24</v>
       </c>
       <c r="AU7" s="3" t="n">
-        <v>4.08370137069058e+23</v>
+        <v>4.083701056087006e+23</v>
       </c>
       <c r="AV7" s="2" t="n">
         <v>4.738407978556136</v>
@@ -2955,25 +2955,25 @@
         <v>1.051939352000445</v>
       </c>
       <c r="AX7" s="2" t="n">
-        <v>0.1859305175663731</v>
+        <v>0.1859305318902437</v>
       </c>
       <c r="AY7" s="2" t="n">
-        <v>0.05355073783901342</v>
+        <v>0.05355074364974851</v>
       </c>
       <c r="AZ7" s="2" t="n">
-        <v>2.031985336724368</v>
+        <v>2.031985116235768</v>
       </c>
       <c r="BA7" s="2" t="n">
-        <v>25.41814661241121</v>
+        <v>25.41814741232349</v>
       </c>
       <c r="BB7" s="3" t="n">
-        <v>2.880147839092471e+23</v>
+        <v>2.880147929731086e+23</v>
       </c>
       <c r="BC7" s="2" t="n">
-        <v>0.2623529266518976</v>
+        <v>0.2623420472890149</v>
       </c>
       <c r="BD7" s="2" t="n">
-        <v>22.25851278425384</v>
+        <v>22.25851036900594</v>
       </c>
       <c r="BE7" t="inlineStr"/>
     </row>
@@ -3042,13 +3042,13 @@
         <v>18.56896321259232</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>10.60366757376142</v>
+        <v>10.60366823249836</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>2.272062324113326</v>
+        <v>2.272062182964871</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>0.1223580604959438</v>
+        <v>0.1223580528946333</v>
       </c>
       <c r="W8" s="2" t="n">
         <v>0.2</v>
@@ -3108,22 +3108,22 @@
         <v>0.1039066067345771</v>
       </c>
       <c r="AP8" s="2" t="n">
-        <v>54.51585733730867</v>
+        <v>54.51585293094176</v>
       </c>
       <c r="AQ8" s="2" t="n">
-        <v>2.953107821348059</v>
+        <v>2.953107582656471</v>
       </c>
       <c r="AR8" s="3" t="n">
-        <v>5.938387451996493e+23</v>
+        <v>5.938386972012958e+23</v>
       </c>
       <c r="AS8" s="3" t="n">
-        <v>3.216806868170546e+22</v>
+        <v>3.216806608164889e+22</v>
       </c>
       <c r="AT8" s="3" t="n">
-        <v>3.729307319853797e+24</v>
+        <v>3.729307018424138e+24</v>
       </c>
       <c r="AU8" s="3" t="n">
-        <v>2.020445630752459e+23</v>
+        <v>2.020445467445392e+23</v>
       </c>
       <c r="AV8" s="2" t="n">
         <v>176.0925657426108</v>
@@ -3132,25 +3132,25 @@
         <v>9.538882053311641</v>
       </c>
       <c r="AX8" s="2" t="n">
-        <v>3.23011641645961</v>
+        <v>3.230116677541063</v>
       </c>
       <c r="AY8" s="2" t="n">
-        <v>1.68848209773271</v>
+        <v>1.688482202627127</v>
       </c>
       <c r="AZ8" s="2" t="n">
-        <v>0.06536862606624197</v>
+        <v>0.06536862200531438</v>
       </c>
       <c r="BA8" s="2" t="n">
-        <v>47.98799465906685</v>
+        <v>47.9879937615111</v>
       </c>
       <c r="BB8" s="3" t="n">
-        <v>5.227310350576718e+23</v>
+        <v>5.22731025280638e+23</v>
       </c>
       <c r="BC8" s="2" t="n">
-        <v>13.60311620566632</v>
+        <v>13.60310914824357</v>
       </c>
       <c r="BD8" s="2" t="n">
-        <v>6.153847107653829</v>
+        <v>6.153846725355332</v>
       </c>
       <c r="BE8" t="inlineStr"/>
     </row>
@@ -3219,13 +3219,13 @@
         <v>2.486864471799392</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>1.077177410724217</v>
+        <v>1.077177645548336</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>2.750780878065064</v>
+        <v>2.750780278396386</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>1.106124161271528</v>
+        <v>1.106123920137085</v>
       </c>
       <c r="W9" s="2" t="n">
         <v>0.2</v>
@@ -3285,22 +3285,22 @@
         <v>0.09487403505582533</v>
       </c>
       <c r="AP9" s="2" t="n">
-        <v>46.63926857927817</v>
+        <v>46.63926122130088</v>
       </c>
       <c r="AQ9" s="2" t="n">
-        <v>18.75622820675455</v>
+        <v>18.75622524770512</v>
       </c>
       <c r="AR9" s="3" t="n">
-        <v>5.080394234430154e+23</v>
+        <v>5.080393432929047e+23</v>
       </c>
       <c r="AS9" s="3" t="n">
-        <v>2.043107375907456e+23</v>
+        <v>2.043107053579552e+23</v>
       </c>
       <c r="AT9" s="3" t="n">
-        <v>3.190487579222137e+24</v>
+        <v>3.190487075879441e+24</v>
       </c>
       <c r="AU9" s="3" t="n">
-        <v>1.283074784750438e+24</v>
+        <v>1.283074582327986e+24</v>
       </c>
       <c r="AV9" s="2" t="n">
         <v>21.65747945676702</v>
@@ -3309,29 +3309,29 @@
         <v>8.709669757872257</v>
       </c>
       <c r="AX9" s="2" t="n">
-        <v>0.4643614729925126</v>
+        <v>0.4643615462518457</v>
       </c>
       <c r="AY9" s="2" t="n">
-        <v>0.1715250654019454</v>
+        <v>0.171525102794321</v>
       </c>
       <c r="AZ9" s="2" t="n">
-        <v>0.6434846977471635</v>
+        <v>0.6434845574678629</v>
       </c>
       <c r="BA9" s="2" t="n">
-        <v>33.90983916689493</v>
+        <v>33.90984120948404</v>
       </c>
       <c r="BB9" s="3" t="n">
-        <v>3.693783299819775e+23</v>
+        <v>3.693783522318075e+23</v>
       </c>
       <c r="BC9" s="2" t="n">
-        <v>37.53904390325319</v>
+        <v>37.53901391981928</v>
       </c>
       <c r="BD9" s="2" t="n">
-        <v>55.31205298391873</v>
+        <v>55.31204092592242</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>LAC &lt; 3 sigma: HVL/TVL/MFP guvenilir degil</t>
+          <t>LAC &lt; 3σ: HVL/TVL/MFP güvenilir değil</t>
         </is>
       </c>
     </row>
@@ -3400,13 +3400,13 @@
         <v>4.72630225289397</v>
       </c>
       <c r="T10" s="2" t="n">
-        <v>0.8527863757903911</v>
+        <v>0.8527865423494825</v>
       </c>
       <c r="U10" s="2" t="n">
-        <v>2.226666134189018</v>
+        <v>2.226665699295326</v>
       </c>
       <c r="V10" s="2" t="n">
-        <v>0.4711222463238791</v>
+        <v>0.4711221543082463</v>
       </c>
       <c r="W10" s="2" t="n">
         <v>0.2</v>
@@ -3466,22 +3466,22 @@
         <v>0.03199999790477622</v>
       </c>
       <c r="AP10" s="2" t="n">
-        <v>35.02344379374568</v>
+        <v>35.02343934375751</v>
       </c>
       <c r="AQ10" s="2" t="n">
-        <v>7.413154973750841</v>
+        <v>7.413154031854545</v>
       </c>
       <c r="AR10" s="3" t="n">
-        <v>3.81508774343622e+23</v>
+        <v>3.81508725870104e+23</v>
       </c>
       <c r="AS10" s="3" t="n">
-        <v>8.075115870130545e+22</v>
+        <v>8.07511484412721e+22</v>
       </c>
       <c r="AT10" s="3" t="n">
-        <v>2.395875102877946e+24</v>
+        <v>2.395874798464253e+24</v>
       </c>
       <c r="AU10" s="3" t="n">
-        <v>5.071220601615798e+23</v>
+        <v>5.071219957279627e+23</v>
       </c>
       <c r="AV10" s="2" t="n">
         <v>13.87905939732096</v>
@@ -3490,25 +3490,25 @@
         <v>2.937678510661091</v>
       </c>
       <c r="AX10" s="2" t="n">
-        <v>0.396279117469294</v>
+        <v>0.3962791678195</v>
       </c>
       <c r="AY10" s="2" t="n">
-        <v>0.1357940088838202</v>
+        <v>0.1357940354059685</v>
       </c>
       <c r="AZ10" s="2" t="n">
-        <v>0.8128028310929724</v>
+        <v>0.8128026723431629</v>
       </c>
       <c r="BA10" s="2" t="n">
-        <v>31.45819057108147</v>
+        <v>31.45819271823463</v>
       </c>
       <c r="BB10" s="3" t="n">
-        <v>3.426726337512406e+23</v>
+        <v>3.42672657140082e+23</v>
       </c>
       <c r="BC10" s="2" t="n">
-        <v>11.33330670945089</v>
+        <v>11.33328496476627</v>
       </c>
       <c r="BD10" s="2" t="n">
-        <v>23.56510288473338</v>
+        <v>23.56509828219578</v>
       </c>
       <c r="BE10" t="inlineStr"/>
     </row>
@@ -3577,13 +3577,13 @@
         <v>2.426398437512705</v>
       </c>
       <c r="T11" s="2" t="n">
-        <v>0.5108042920535788</v>
+        <v>0.5108043375662259</v>
       </c>
       <c r="U11" s="2" t="n">
-        <v>1.814095898955189</v>
+        <v>1.814095737319313</v>
       </c>
       <c r="V11" s="2" t="n">
-        <v>0.7476496320261458</v>
+        <v>0.7476495654105919</v>
       </c>
       <c r="W11" s="2" t="n">
         <v>0.2</v>
@@ -3643,22 +3643,22 @@
         <v>0.03040932029135026</v>
       </c>
       <c r="AP11" s="2" t="n">
-        <v>24.89584820661005</v>
+        <v>24.89584672782507</v>
       </c>
       <c r="AQ11" s="2" t="n">
-        <v>10.26144449507104</v>
+        <v>10.26144388555294</v>
       </c>
       <c r="AR11" s="3" t="n">
-        <v>2.71189337961242e+23</v>
+        <v>2.711893218529047e+23</v>
       </c>
       <c r="AS11" s="3" t="n">
-        <v>1.117774464260065e+23</v>
+        <v>1.117774397865537e+23</v>
       </c>
       <c r="AT11" s="3" t="n">
-        <v>1.7030690423966e+24</v>
+        <v>1.703068941236241e+24</v>
       </c>
       <c r="AU11" s="3" t="n">
-        <v>7.01964109697502e+23</v>
+        <v>7.019640680016345e+23</v>
       </c>
       <c r="AV11" s="2" t="n">
         <v>6.772974748003384</v>
@@ -3667,29 +3667,29 @@
         <v>2.791650393526319</v>
       </c>
       <c r="AX11" s="2" t="n">
-        <v>0.2720523796495957</v>
+        <v>0.2720523958091977</v>
       </c>
       <c r="AY11" s="2" t="n">
-        <v>0.08133826306585649</v>
+        <v>0.08133827031309329</v>
       </c>
       <c r="AZ11" s="2" t="n">
-        <v>1.35697211504096</v>
+        <v>1.356971994134796</v>
       </c>
       <c r="BA11" s="2" t="n">
-        <v>27.44711370655606</v>
+        <v>27.44711452176567</v>
       </c>
       <c r="BB11" s="3" t="n">
-        <v>2.989801565809512e+23</v>
+        <v>2.989801654609924e+23</v>
       </c>
       <c r="BC11" s="2" t="n">
-        <v>-9.295205052240533</v>
+        <v>-9.295213134034318</v>
       </c>
       <c r="BD11" s="2" t="n">
-        <v>37.38624251999208</v>
+        <v>37.38623918887929</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>LAC &lt; 3 sigma: HVL/TVL/MFP guvenilir degil</t>
+          <t>LAC &lt; 3σ: HVL/TVL/MFP güvenilir değil</t>
         </is>
       </c>
     </row>
@@ -3758,13 +3758,13 @@
         <v>4.014687427582307</v>
       </c>
       <c r="T12" s="2" t="n">
-        <v>0.3586335710374853</v>
+        <v>0.3586335981033563</v>
       </c>
       <c r="U12" s="2" t="n">
-        <v>1.98440994091548</v>
+        <v>1.984409791153206</v>
       </c>
       <c r="V12" s="2" t="n">
-        <v>0.4942875321455638</v>
+        <v>0.4942874948419686</v>
       </c>
       <c r="W12" s="2" t="n">
         <v>0.2</v>
@@ -3824,22 +3824,22 @@
         <v>0.0141175893920553</v>
       </c>
       <c r="AP12" s="2" t="n">
-        <v>26.0057754835553</v>
+        <v>26.00577438549107</v>
       </c>
       <c r="AQ12" s="2" t="n">
-        <v>6.479442794883083</v>
+        <v>6.479442521295995</v>
       </c>
       <c r="AR12" s="3" t="n">
-        <v>2.832797251182455e+23</v>
+        <v>2.83279713157082e+23</v>
       </c>
       <c r="AS12" s="3" t="n">
-        <v>7.058027456303109e+22</v>
+        <v>7.058027158285944e+22</v>
       </c>
       <c r="AT12" s="3" t="n">
-        <v>1.778996673742582e+24</v>
+        <v>1.778996598626475e+24</v>
       </c>
       <c r="AU12" s="3" t="n">
-        <v>4.432471416723907e+23</v>
+        <v>4.432471229567854e+23</v>
       </c>
       <c r="AV12" s="2" t="n">
         <v>5.201720485954501</v>
@@ -3848,25 +3848,25 @@
         <v>1.296029427964047</v>
       </c>
       <c r="AX12" s="2" t="n">
-        <v>0.2000217409107372</v>
+        <v>0.2000217493564276</v>
       </c>
       <c r="AY12" s="2" t="n">
-        <v>0.05710725653463142</v>
+        <v>0.05710726084448348</v>
       </c>
       <c r="AZ12" s="2" t="n">
-        <v>1.932744830760687</v>
+        <v>1.932744684897548</v>
       </c>
       <c r="BA12" s="2" t="n">
-        <v>26.21008386156128</v>
+        <v>26.21008473293036</v>
       </c>
       <c r="BB12" s="3" t="n">
-        <v>2.855052469527121e+23</v>
+        <v>2.855052564444956e+23</v>
       </c>
       <c r="BC12" s="2" t="n">
-        <v>-0.7795029542259957</v>
+        <v>-0.7795104423397278</v>
       </c>
       <c r="BD12" s="2" t="n">
-        <v>24.72118299623447</v>
+        <v>24.72118113054103</v>
       </c>
       <c r="BE12" t="inlineStr"/>
     </row>
@@ -3935,13 +3935,13 @@
         <v>5.419111152478443</v>
       </c>
       <c r="T13" s="2" t="n">
-        <v>0.3343770710786853</v>
+        <v>0.3343771199217104</v>
       </c>
       <c r="U13" s="2" t="n">
-        <v>2.099834227483437</v>
+        <v>2.099833920757139</v>
       </c>
       <c r="V13" s="2" t="n">
-        <v>0.3874868347225305</v>
+        <v>0.3874867781216805</v>
       </c>
       <c r="W13" s="2" t="n">
         <v>0.2</v>
@@ -4001,22 +4001,22 @@
         <v>0.01032099685219263</v>
       </c>
       <c r="AP13" s="2" t="n">
-        <v>27.41445242844401</v>
+        <v>27.41444997949892</v>
       </c>
       <c r="AQ13" s="2" t="n">
-        <v>5.061384852047949</v>
+        <v>5.061384399912215</v>
       </c>
       <c r="AR13" s="3" t="n">
-        <v>2.9862437876954e+23</v>
+        <v>2.986243520932929e+23</v>
       </c>
       <c r="AS13" s="3" t="n">
-        <v>5.51334341293705e+22</v>
+        <v>5.513342920427659e+22</v>
       </c>
       <c r="AT13" s="3" t="n">
-        <v>1.875361098672711e+24</v>
+        <v>1.87536093114588e+24</v>
       </c>
       <c r="AU13" s="3" t="n">
-        <v>3.462422589469427e+23</v>
+        <v>3.462422280169695e+23</v>
       </c>
       <c r="AV13" s="2" t="n">
         <v>5.131994436526965</v>
@@ -4025,25 +4025,25 @@
         <v>0.947492895203022</v>
       </c>
       <c r="AX13" s="2" t="n">
-        <v>0.1872003261754824</v>
+        <v>0.1872003428981714</v>
       </c>
       <c r="AY13" s="2" t="n">
-        <v>0.05324475654119191</v>
+        <v>0.0532447643187437</v>
       </c>
       <c r="AZ13" s="2" t="n">
-        <v>2.072950691038366</v>
+        <v>2.072950388238991</v>
       </c>
       <c r="BA13" s="2" t="n">
-        <v>26.11106350171183</v>
+        <v>26.11106498328598</v>
       </c>
       <c r="BB13" s="3" t="n">
-        <v>2.844266226933817e+23</v>
+        <v>2.844266388321013e+23</v>
       </c>
       <c r="BC13" s="2" t="n">
-        <v>4.991711374171827</v>
+        <v>4.991696037856935</v>
       </c>
       <c r="BD13" s="2" t="n">
-        <v>19.38406243666072</v>
+        <v>19.38405960519829</v>
       </c>
       <c r="BE13" t="inlineStr"/>
     </row>
@@ -6622,14 +6622,14 @@
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
     <col width="24" customWidth="1" min="8" max="8"/>
     <col width="21" customWidth="1" min="9" max="9"/>
     <col width="21" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="21" customWidth="1" min="11" max="11"/>
     <col width="21" customWidth="1" min="12" max="12"/>
     <col width="24" customWidth="1" min="13" max="13"/>
   </cols>
@@ -6716,34 +6716,34 @@
         <v>80.89906428571429</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.8091065333821519</v>
+        <v>0.8091066252691731</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>71.40601677255438</v>
+        <v>71.40602488185262</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>2.145752233243117</v>
+        <v>2.145752499648045</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>33.27784805081173</v>
+        <v>33.2778476984484</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>3.770736065641922e+23</v>
+        <v>3.770736025715389e+23</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>5.154008617644307</v>
+        <v>5.154009202964633</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>0.1344870045787303</v>
+        <v>0.1344869893055761</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>0.4467561589073295</v>
+        <v>0.4467561081710095</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>0.1940237345697455</v>
+        <v>0.1940237125352417</v>
       </c>
       <c r="M2" s="3" t="n">
-        <v>2.401958873813904e+24</v>
+        <v>2.401958848380703e+24</v>
       </c>
     </row>
     <row r="3">
@@ -6761,34 +6761,34 @@
         <v>295.4176231113203</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.1461871182359844</v>
+        <v>0.1461871446496136</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>12.90144052236912</v>
+        <v>12.90144285344911</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.4279947387244372</v>
+        <v>0.4279948024046465</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>30.14392317255951</v>
+        <v>30.14392413404001</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>3.415628861973148e+23</v>
+        <v>3.415628970919171e+23</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>0.9312119431632206</v>
+        <v>0.9312121114180388</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>0.7443495389517917</v>
+        <v>0.7443494044599881</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>2.472675645860412</v>
+        <v>2.472675199088311</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>1.073869388533736</v>
+        <v>1.073869194503078</v>
       </c>
       <c r="M3" s="3" t="n">
-        <v>2.175755585076895e+24</v>
+        <v>2.175755654475512e+24</v>
       </c>
     </row>
     <row r="4">
@@ -6806,34 +6806,34 @@
         <v>359.5183270178899</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.1212976334572946</v>
+        <v>0.1212976516304759</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>10.70487073305073</v>
+        <v>10.7048723368871</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.3742958260370648</v>
+        <v>0.3742958680525469</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>28.60002700642107</v>
+        <v>28.60002808095189</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>3.240688915544655e+23</v>
+        <v>3.240689037300489e+23</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>0.7726659251229667</v>
+        <v>0.7726660408861314</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.8970852188798589</v>
+        <v>0.8970850844758363</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>2.980052592105182</v>
+        <v>2.980052145624684</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>1.294220396532763</v>
+        <v>1.294220202628746</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>2.064318839201945e+24</v>
+        <v>2.064318916760411e+24</v>
       </c>
     </row>
     <row r="5">
@@ -6851,34 +6851,34 @@
         <v>661.657</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.07923019671215378</v>
+        <v>0.07923020228576637</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>6.992296467650345</v>
+        <v>6.992296959537949</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.2669193487862835</v>
+        <v>0.2669193626578095</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>26.19628925158559</v>
+        <v>26.19628973302349</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>2.968319721759537e+23</v>
+        <v>2.9683197763116e+23</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>0.5046963530564196</v>
+        <v>0.5046963885603317</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>1.373394470481658</v>
+        <v>1.373394373867381</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>4.562317676855972</v>
+        <v>4.562317355910292</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>1.981389391748212</v>
+        <v>1.981389252363274</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>1.890819662760825e+24</v>
+        <v>1.890819697510489e+24</v>
       </c>
     </row>
     <row r="6">
@@ -6896,34 +6896,34 @@
         <v>1173.228</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.05729122902391755</v>
+        <v>0.05729123209776895</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>5.056118436593945</v>
+        <v>5.056118707870315</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.1984537421446335</v>
+        <v>0.1984537492477799</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>25.47756662058322</v>
+        <v>25.47756707562872</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>2.886880761470529e+23</v>
+        <v>2.88688081303205e+23</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>0.3649451288823548</v>
+        <v>0.3649451484627882</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>1.899318899481437</v>
+        <v>1.899318797577117</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>6.309400813337932</v>
+        <v>6.309400474819109</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>2.740137957348553</v>
+        <v>2.740137810331696</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>1.838943045056727e+24</v>
+        <v>1.838943077901416e+24</v>
       </c>
     </row>
     <row r="7">
@@ -6941,34 +6941,34 @@
         <v>1332.492</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0.05355073783901342</v>
+        <v>0.05355074364974851</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>4.72600915522357</v>
+        <v>4.726009668037928</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.1859305175663731</v>
+        <v>0.1859305318902437</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>25.41814661241121</v>
+        <v>25.41814741232349</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>2.880147839092471e+23</v>
+        <v>2.880147929731086e+23</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>0.3411182000345155</v>
+        <v>0.341118237048898</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>2.031985336724368</v>
+        <v>2.031985116235768</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>6.750109178463837</v>
+        <v>6.750108446016561</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>2.931535168451336</v>
+        <v>2.931534850353527</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>1.834654173501904e+24</v>
+        <v>1.834654231238702e+24</v>
       </c>
     </row>
     <row r="8">
@@ -6986,34 +6986,34 @@
         <v>80.89906428571429</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>1.68848209773271</v>
+        <v>1.688482202627127</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>155.0068093412279</v>
+        <v>155.0068189707935</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>3.23011641645961</v>
+        <v>3.230116677541063</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>47.98799465906685</v>
+        <v>47.9879937615111</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>5.227310350576718e+23</v>
+        <v>5.22731025280638e+23</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>10.60366757376142</v>
+        <v>10.60366823249836</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.06536862606624197</v>
+        <v>0.06536862200531438</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0.2171498754536356</v>
+        <v>0.2171498619635261</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>0.09430699265549232</v>
+        <v>0.09430698679681221</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>3.282750900162179e+24</v>
+        <v>3.282750838762406e+24</v>
       </c>
     </row>
     <row r="9">
@@ -7031,34 +7031,34 @@
         <v>295.4176231113203</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>0.1715250654019454</v>
+        <v>0.171525102794321</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>15.74642286447853</v>
+        <v>15.74642629719057</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.4643614729925126</v>
+        <v>0.4643615462518457</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>33.90983916689493</v>
+        <v>33.90984120948404</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>3.693783299819775e+23</v>
+        <v>3.693783522318075e+23</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>1.077177410724217</v>
+        <v>1.077177645548336</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.6434846977471635</v>
+        <v>0.6434845574678629</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>2.137609896076405</v>
+        <v>2.137609430078656</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>0.9283521823277665</v>
+        <v>0.9283519799475151</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>2.319695912286819e+24</v>
+        <v>2.319696052015751e+24</v>
       </c>
     </row>
     <row r="10">
@@ -7076,34 +7076,34 @@
         <v>359.5183270178899</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>0.1357940088838202</v>
+        <v>0.1357940354059685</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>12.46622399668903</v>
+        <v>12.46622643148747</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0.396279117469294</v>
+        <v>0.3962791678195</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>31.45819057108147</v>
+        <v>31.45819271823463</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>3.426726337512406e+23</v>
+        <v>3.42672657140082e+23</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>0.8527863757903911</v>
+        <v>0.8527865423494825</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.8128028310929724</v>
+        <v>0.8128026723431629</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>2.700072560211733</v>
+        <v>2.700072032856281</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>1.172626613638341</v>
+        <v>1.172626384610778</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>2.151984139957791e+24</v>
+        <v>2.151984286839715e+24</v>
       </c>
     </row>
     <row r="11">
@@ -7121,34 +7121,34 @@
         <v>661.657</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>0.08133826306585649</v>
+        <v>0.08133827031309329</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>7.467052598381609</v>
+        <v>7.467053263695772</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>0.2720523796495957</v>
+        <v>0.2720523958091977</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>27.44711370655606</v>
+        <v>27.44711452176567</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>2.989801565809512e+23</v>
+        <v>2.989801654609924e+23</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>0.5108042920535788</v>
+        <v>0.5108043375662259</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>1.35697211504096</v>
+        <v>1.356971994134796</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>4.507763792933293</v>
+        <v>4.50776339129171</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>1.957696940994202</v>
+        <v>1.957696766563479</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>1.877595383328374e+24</v>
+        <v>1.877595439095032e+24</v>
       </c>
     </row>
     <row r="12">
@@ -7166,34 +7166,34 @@
         <v>1173.228</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>0.05710725653463142</v>
+        <v>0.05710726084448348</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>5.242586603405906</v>
+        <v>5.242586999060926</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>0.2000217409107372</v>
+        <v>0.2000217493564276</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>26.21008386156128</v>
+        <v>26.21008473293036</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>2.855052469527121e+23</v>
+        <v>2.855052564444956e+23</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>0.3586335710374853</v>
+        <v>0.3586335981033563</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>1.932744830760687</v>
+        <v>1.932744684897548</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>6.420439353552246</v>
+        <v>6.420438869005389</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>2.788361382642222</v>
+        <v>2.788361172206195</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>1.792972950863032e+24</v>
+        <v>1.792973010471432e+24</v>
       </c>
     </row>
     <row r="13">
@@ -7211,34 +7211,34 @@
         <v>1332.492</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>0.05324475654119191</v>
+        <v>0.0532447643187437</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>4.887999604309189</v>
+        <v>4.888000318307571</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>0.1872003261754824</v>
+        <v>0.1872003428981714</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>26.11106350171183</v>
+        <v>26.11106498328598</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>2.844266226933817e+23</v>
+        <v>2.844266388321013e+23</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>0.3343770710786853</v>
+        <v>0.3343771199217104</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>2.072950691038366</v>
+        <v>2.072950388238991</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>6.88619313987652</v>
+        <v>6.886192133998771</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>2.9906356819684</v>
+        <v>2.990635245121244</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>1.786199190514437e+24</v>
+        <v>1.786199291865596e+24</v>
       </c>
     </row>
   </sheetData>
@@ -7319,13 +7319,13 @@
         <v>80.89906428571429</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>2.352557616883219</v>
+        <v>2.35255765896867</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>26.70152895162454</v>
+        <v>26.70152942929441</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.02595908203667767</v>
+        <v>0.02595908157228962</v>
       </c>
     </row>
     <row r="3">
@@ -7346,13 +7346,13 @@
         <v>295.4176231113203</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.4163622880996919</v>
+        <v>0.4163623946355609</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>4.725711969931503</v>
+        <v>4.725713179113615</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.1466757146796639</v>
+        <v>0.1466756771493179</v>
       </c>
     </row>
     <row r="4">
@@ -7373,13 +7373,13 @@
         <v>359.5183270178899</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.2821304751238382</v>
+        <v>0.2821305555687182</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>3.202180892655563</v>
+        <v>3.202181805704951</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.2164609695066663</v>
+        <v>0.2164609077863869</v>
       </c>
     </row>
     <row r="5">
@@ -7400,13 +7400,13 @@
         <v>661.657</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.1102033533310854</v>
+        <v>0.1102033739037272</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>1.250808060307819</v>
+        <v>1.250808293807304</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.554159509005214</v>
+        <v>0.5541594055553406</v>
       </c>
     </row>
     <row r="6">
@@ -7427,13 +7427,13 @@
         <v>1173.228</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.06166367792142712</v>
+        <v>0.06166369276333716</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.6998827444081978</v>
+        <v>0.6998829128638767</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.9903761538599614</v>
+        <v>0.9903759154851071</v>
       </c>
     </row>
     <row r="7">
@@ -7454,13 +7454,13 @@
         <v>1332.492</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.05610115372288973</v>
+        <v>0.05610117871916188</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.6367480947547984</v>
+        <v>0.6367483784624873</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>1.088573623179611</v>
+        <v>1.088573138158028</v>
       </c>
     </row>
     <row r="8">
@@ -7481,13 +7481,13 @@
         <v>80.89906428571429</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.1996495265144275</v>
+        <v>0.1996495455767022</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.4591939109831832</v>
+        <v>0.459193954826415</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>1.509486872497597</v>
+        <v>1.509486728373786</v>
       </c>
     </row>
     <row r="9">
@@ -7508,13 +7508,13 @@
         <v>295.4176231113203</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.1103931810472376</v>
+        <v>0.1103931815987268</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.2539043164086464</v>
+        <v>0.2539043176770715</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>2.729954300754617</v>
+        <v>2.729954287116635</v>
       </c>
     </row>
     <row r="10">
@@ -7535,13 +7535,13 @@
         <v>359.5183270178899</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.1020581609644876</v>
+        <v>0.1020581627180894</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0.2347337702183215</v>
+        <v>0.2347337742516055</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>2.952907798120663</v>
+        <v>2.952907747382689</v>
       </c>
     </row>
     <row r="11">
@@ -7562,13 +7562,13 @@
         <v>661.657</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0.07883704400614537</v>
+        <v>0.07883704636894012</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>0.1813252012141343</v>
+        <v>0.1813252066485623</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>3.822674266559227</v>
+        <v>3.822674151991329</v>
       </c>
     </row>
     <row r="12">
@@ -7589,13 +7589,13 @@
         <v>1173.228</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>0.05993790771013759</v>
+        <v>0.059937908254028</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>0.1378571877333165</v>
+        <v>0.1378571889842644</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>5.028008999435216</v>
+        <v>5.028008953809903</v>
       </c>
     </row>
     <row r="13">
@@ -7616,13 +7616,13 @@
         <v>1332.492</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.05619604576989413</v>
+        <v>0.05619604768884361</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>0.1292509052707565</v>
+        <v>0.1292509096843403</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>5.36280329416596</v>
+        <v>5.362803111040117</v>
       </c>
     </row>
   </sheetData>

--- a/examples/sentetik_ornek/sonuclar.xlsx
+++ b/examples/sentetik_ornek/sonuclar.xlsx
@@ -547,52 +547,52 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.354 ± 0.052</t>
+          <t>0.334 ± 0.044</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>64.6 ± 5.2</t>
+          <t>66.6 ± 4.4</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>5.20 ± 0.73</t>
+          <t>5.49 ± 0.67</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0.82 ± 0.11</t>
+          <t>0.86 ± 0.11</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0.133 ± 0.019</t>
+          <t>0.126 ± 0.015</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.443 ± 0.062</t>
+          <t>0.420 ± 0.051</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0.192 ± 0.027</t>
+          <t>0.182 ± 0.022</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>33.6 ± 4.7</t>
+          <t>35.4 ± 4.3</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>(3.80 ± 0.53)e23</t>
+          <t>(4.02 ± 0.49)e23</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2.02 ± 0.28</t>
+          <t>2.13 ± 0.26</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -613,17 +613,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.870 ± 0.180</t>
+          <t>0.864 ± 0.172</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>13 ± 18</t>
+          <t>14 ± 17</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.7 ± 1.0</t>
+          <t>0.73 ± 1.00</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -633,32 +633,32 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1.0 ± 1.5</t>
+          <t>0.9 ± 1.3</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3.3 ± 4.9</t>
+          <t>3.1 ± 4.3</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>1.4 ± 2.1</t>
+          <t>1.4 ± 1.9</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>23 ± 34</t>
+          <t>24 ± 32</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>(2.6 ± 3.8)e23</t>
+          <t>(2.7 ± 3.7)e23</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>1.49 ± 2.23</t>
+          <t>1.57 ± 2.14</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -683,37 +683,37 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.885 ± 0.073</t>
+          <t>0.882 ± 0.073</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>11.5 ± 7.3</t>
+          <t>11.8 ± 7.3</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0.61 ± 0.41</t>
+          <t>0.63 ± 0.41</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0.096 ± 0.065</t>
+          <t>0.099 ± 0.065</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1.13 ± 0.76</t>
+          <t>1.10 ± 0.72</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3.8 ± 2.5</t>
+          <t>3.7 ± 2.4</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>1.6 ± 1.1</t>
+          <t>1.6 ± 1.0</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -728,14 +728,10 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>1.59 ± 1.07</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>LAC &lt; 3σ: HVL/TVL/MFP güvenilir değil</t>
-        </is>
-      </c>
+          <t>1.63 ± 1.07</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -753,52 +749,52 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.900 ± 0.062</t>
+          <t>0.894 ± 0.062</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>10.0 ± 6.2</t>
+          <t>10.6 ± 6.2</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0.53 ± 0.34</t>
+          <t>0.56 ± 0.35</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0.083 ± 0.054</t>
+          <t>0.088 ± 0.054</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1.31 ± 0.85</t>
+          <t>1.24 ± 0.77</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>4.3 ± 2.8</t>
+          <t>4.1 ± 2.5</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>1.9 ± 1.2</t>
+          <t>1.8 ± 1.1</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>27 ± 18</t>
+          <t>29 ± 18</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>(3.1 ± 2.0)e23</t>
+          <t>(3.3 ± 2.0)e23</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2.10 ± 1.36</t>
+          <t>2.22 ± 1.38</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -819,52 +815,52 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.931 ± 0.058</t>
+          <t>0.934 ± 0.059</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>6.9 ± 5.8</t>
+          <t>6.6 ± 5.9</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0.36 ± 0.31</t>
+          <t>0.34 ± 0.31</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0.056 ± 0.049</t>
+          <t>0.053 ± 0.049</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1.9 ± 1.7</t>
+          <t>2.0 ± 1.9</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>6.5 ± 5.7</t>
+          <t>6.8 ± 6.3</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2.8 ± 2.5</t>
+          <t>2.9 ± 2.7</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>25 ± 22</t>
+          <t>24 ± 22</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>(2.8 ± 2.5)e23</t>
+          <t>(2.7 ± 2.5)e23</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>1.95 ± 1.71</t>
+          <t>1.86 ± 1.73</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -889,52 +885,52 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.934 ± 0.028</t>
+          <t>0.937 ± 0.029</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>6.6 ± 2.8</t>
+          <t>6.3 ± 2.9</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0.34 ± 0.15</t>
+          <t>0.33 ± 0.15</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0.054 ± 0.024</t>
+          <t>0.051 ± 0.024</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2.03 ± 0.90</t>
+          <t>2.13 ± 0.99</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>6.7 ± 3.0</t>
+          <t>7.1 ± 3.3</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2.9 ± 1.3</t>
+          <t>3.1 ± 1.4</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>25 ± 11</t>
+          <t>24 ± 11</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>(2.9 ± 1.3)e23</t>
+          <t>(2.8 ± 1.3)e23</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2.01 ± 0.89</t>
+          <t>1.91 ± 0.89</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -955,52 +951,52 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.090 ± 0.023</t>
+          <t>0.093 ± 0.024</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>91.0 ± 2.3</t>
+          <t>90.7 ± 2.4</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>12.0 ± 1.3</t>
+          <t>11.9 ± 1.3</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1.92 ± 0.21</t>
+          <t>1.89 ± 0.21</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.0575 ± 0.0062</t>
+          <t>0.0582 ± 0.0064</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.191 ± 0.021</t>
+          <t>0.193 ± 0.021</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.0830 ± 0.0090</t>
+          <t>0.0840 ± 0.0092</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>54.5 ± 5.9</t>
+          <t>53.9 ± 5.9</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>(5.94 ± 0.64)e23</t>
+          <t>(5.87 ± 0.64)e23</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2.27 ± 0.24</t>
+          <t>2.24 ± 0.25</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1021,52 +1017,52 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.744 ± 0.177</t>
+          <t>0.738 ± 0.185</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>26 ± 18</t>
+          <t>26 ± 19</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>1.5 ± 1.2</t>
+          <t>1.5 ± 1.3</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.24 ± 0.19</t>
+          <t>0.24 ± 0.20</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.47 ± 0.38</t>
+          <t>0.46 ± 0.38</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1.6 ± 1.3</t>
+          <t>1.5 ± 1.3</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.67 ± 0.54</t>
+          <t>0.66 ± 0.54</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>47 ± 38</t>
+          <t>48 ± 40</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>(5.1 ± 4.1)e23</t>
+          <t>(5.2 ± 4.3)e23</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2.75 ± 2.21</t>
+          <t>2.82 ± 2.33</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1091,27 +1087,27 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.827 ± 0.066</t>
+          <t>0.824 ± 0.067</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>17.3 ± 6.6</t>
+          <t>17.6 ± 6.7</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0.95 ± 0.40</t>
+          <t>0.97 ± 0.41</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0.151 ± 0.064</t>
+          <t>0.154 ± 0.065</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.73 ± 0.31</t>
+          <t>0.72 ± 0.30</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1121,22 +1117,22 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>1.05 ± 0.45</t>
+          <t>1.03 ± 0.44</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>35 ± 15</t>
+          <t>36 ± 15</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>(3.8 ± 1.6)e23</t>
+          <t>(3.9 ± 1.6)e23</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2.23 ± 0.94</t>
+          <t>2.27 ± 0.96</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1157,52 +1153,52 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.911 ± 0.070</t>
+          <t>0.906 ± 0.071</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>8.9 ± 7.0</t>
+          <t>9.4 ± 7.1</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0.46 ± 0.38</t>
+          <t>0.49 ± 0.39</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0.074 ± 0.061</t>
+          <t>0.079 ± 0.063</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1.5 ± 1.2</t>
+          <t>1.4 ± 1.1</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>5.0 ± 4.1</t>
+          <t>4.7 ± 3.7</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2.2 ± 1.8</t>
+          <t>2.0 ± 1.6</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>25 ± 21</t>
+          <t>27 ± 21</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>(2.7 ± 2.2)e23</t>
+          <t>(2.9 ± 2.3)e23</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>1.81 ± 1.50</t>
+          <t>1.94 ± 1.54</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1227,52 +1223,52 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0.931 ± 0.033</t>
+          <t>0.934 ± 0.033</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>6.9 ± 3.3</t>
+          <t>6.6 ± 3.3</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>0.36 ± 0.18</t>
+          <t>0.34 ± 0.18</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>0.057 ± 0.028</t>
+          <t>0.054 ± 0.028</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1.95 ± 0.97</t>
+          <t>2.0 ± 1.1</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>6.5 ± 3.2</t>
+          <t>6.8 ± 3.6</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2.8 ± 1.4</t>
+          <t>3.0 ± 1.6</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>26 ± 13</t>
+          <t>25 ± 13</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>(2.8 ± 1.4)e23</t>
+          <t>(2.7 ± 1.4)e23</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>1.98 ± 0.99</t>
+          <t>1.89 ± 1.00</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1293,52 +1289,52 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0.932 ± 0.024</t>
+          <t>0.935 ± 0.024</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>6.8 ± 2.4</t>
+          <t>6.5 ± 2.4</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>0.35 ± 0.13</t>
+          <t>0.34 ± 0.13</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>0.056 ± 0.021</t>
+          <t>0.053 ± 0.021</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>1.97 ± 0.73</t>
+          <t>2.07 ± 0.80</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>6.6 ± 2.4</t>
+          <t>6.9 ± 2.7</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2.8 ± 1.1</t>
+          <t>3.0 ± 1.2</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>27 ± 10</t>
+          <t>26 ± 10</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>(3.0 ± 1.1)e23</t>
+          <t>(2.9 ± 1.1)e23</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2.10 ± 0.77</t>
+          <t>2.01 ± 0.78</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1377,7 +1373,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Spektrumlarda tespit edilemeyen çizgiler (analiz dışı bırakıldı): Am-241 59.5 (en yüksek 0.8σ); Co-57 122 (en yüksek 2.5σ)</t>
+          <t>Spektrumlarda tespit edilemeyen çizgiler (analiz dışı bırakıldı): Co-57 122 (en yüksek 2.5σ)</t>
         </is>
       </c>
     </row>
@@ -1554,7 +1550,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BE13"/>
+  <dimension ref="A1:BG13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1563,57 +1559,59 @@
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
-    <col width="21" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="8" max="8"/>
+    <col width="21" customWidth="1" min="9" max="9"/>
     <col width="22" customWidth="1" min="10" max="10"/>
     <col width="21" customWidth="1" min="11" max="11"/>
     <col width="22" customWidth="1" min="12" max="12"/>
-    <col width="23" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
     <col width="22" customWidth="1" min="14" max="14"/>
     <col width="22" customWidth="1" min="15" max="15"/>
     <col width="26" customWidth="1" min="16" max="16"/>
-    <col width="20" customWidth="1" min="17" max="17"/>
+    <col width="18" customWidth="1" min="17" max="17"/>
     <col width="20" customWidth="1" min="18" max="18"/>
     <col width="20" customWidth="1" min="19" max="19"/>
-    <col width="21" customWidth="1" min="20" max="20"/>
-    <col width="24" customWidth="1" min="21" max="21"/>
-    <col width="26" customWidth="1" min="22" max="22"/>
-    <col width="10" customWidth="1" min="23" max="23"/>
-    <col width="23" customWidth="1" min="24" max="24"/>
-    <col width="21" customWidth="1" min="25" max="25"/>
+    <col width="20" customWidth="1" min="20" max="20"/>
+    <col width="21" customWidth="1" min="21" max="21"/>
+    <col width="24" customWidth="1" min="22" max="22"/>
+    <col width="26" customWidth="1" min="23" max="23"/>
+    <col width="10" customWidth="1" min="24" max="24"/>
+    <col width="23" customWidth="1" min="25" max="25"/>
     <col width="21" customWidth="1" min="26" max="26"/>
-    <col width="22" customWidth="1" min="27" max="27"/>
-    <col width="21" customWidth="1" min="28" max="28"/>
+    <col width="21" customWidth="1" min="27" max="27"/>
+    <col width="22" customWidth="1" min="28" max="28"/>
     <col width="22" customWidth="1" min="29" max="29"/>
     <col width="22" customWidth="1" min="30" max="30"/>
-    <col width="23" customWidth="1" min="31" max="31"/>
-    <col width="22" customWidth="1" min="32" max="32"/>
-    <col width="23" customWidth="1" min="33" max="33"/>
+    <col width="22" customWidth="1" min="31" max="31"/>
+    <col width="23" customWidth="1" min="32" max="32"/>
+    <col width="13" customWidth="1" min="33" max="33"/>
     <col width="21" customWidth="1" min="34" max="34"/>
     <col width="22" customWidth="1" min="35" max="35"/>
     <col width="21" customWidth="1" min="36" max="36"/>
     <col width="22" customWidth="1" min="37" max="37"/>
-    <col width="11" customWidth="1" min="38" max="38"/>
+    <col width="21" customWidth="1" min="38" max="38"/>
     <col width="22" customWidth="1" min="39" max="39"/>
-    <col width="21" customWidth="1" min="40" max="40"/>
+    <col width="11" customWidth="1" min="40" max="40"/>
     <col width="22" customWidth="1" min="41" max="41"/>
-    <col width="20" customWidth="1" min="42" max="42"/>
-    <col width="20" customWidth="1" min="43" max="43"/>
-    <col width="24" customWidth="1" min="44" max="44"/>
-    <col width="24" customWidth="1" min="45" max="45"/>
+    <col width="22" customWidth="1" min="42" max="42"/>
+    <col width="22" customWidth="1" min="43" max="43"/>
+    <col width="20" customWidth="1" min="44" max="44"/>
+    <col width="20" customWidth="1" min="45" max="45"/>
     <col width="24" customWidth="1" min="46" max="46"/>
     <col width="24" customWidth="1" min="47" max="47"/>
-    <col width="20" customWidth="1" min="48" max="48"/>
-    <col width="20" customWidth="1" min="49" max="49"/>
-    <col width="21" customWidth="1" min="50" max="50"/>
-    <col width="21" customWidth="1" min="51" max="51"/>
+    <col width="24" customWidth="1" min="48" max="48"/>
+    <col width="24" customWidth="1" min="49" max="49"/>
+    <col width="20" customWidth="1" min="50" max="50"/>
+    <col width="20" customWidth="1" min="51" max="51"/>
     <col width="21" customWidth="1" min="52" max="52"/>
-    <col width="20" customWidth="1" min="53" max="53"/>
-    <col width="24" customWidth="1" min="54" max="54"/>
-    <col width="21" customWidth="1" min="55" max="55"/>
-    <col width="20" customWidth="1" min="56" max="56"/>
-    <col width="39" customWidth="1" min="57" max="57"/>
+    <col width="21" customWidth="1" min="53" max="53"/>
+    <col width="21" customWidth="1" min="54" max="54"/>
+    <col width="20" customWidth="1" min="55" max="55"/>
+    <col width="24" customWidth="1" min="56" max="56"/>
+    <col width="21" customWidth="1" min="57" max="57"/>
+    <col width="20" customWidth="1" min="58" max="58"/>
+    <col width="39" customWidth="1" min="59" max="59"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1699,205 +1697,215 @@
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
+          <t>I0_olcek_carpani</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
           <t>RPE_yuzde</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>u_RPE_yuzde</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>L_anlamlilik_sigma</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>LAC_kuram_cm-1</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Kalinlik_cikarsanan_mm</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>u_Kalinlik_cikarsanan_mm</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>x_cm</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>u_x_cm</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>LAC_cm-1</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>u_LAC_cm-1</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>LAC_anlamlilik_sigma</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Katki_ist_I0</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Katki_ist_I</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>Katki_model</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>Katki_kalinlik</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>Katki_olcek</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>HVL_cm</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>u_HVL_cm</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>TVL_cm</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>u_TVL_cm</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>MFP_cm</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>u_MFP_cm</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>rho_g_cm3</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>u_rho_g_cm3</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>MAC_cm2_g</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>u_MAC_cm2_g</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>Zeff</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>u_Zeff</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>Neff_e_g</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>u_Neff_e_g</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>Ne_e_cm3</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>u_Ne_e_cm3</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>sigma_a_barn</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>u_sigma_a_barn</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>sigma_e_barn</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>MAC_kuram_cm2_g</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>HVL_kuram_cm</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>Zeff_kuram</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>Neff_kuram_e_g</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>Sapma_MAC_yuzde</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>u_Sapma_MAC_yuzde</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>Not</t>
         </is>
@@ -1923,34 +1931,34 @@
         <v>80.89906428571429</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>4.225420233483845</v>
+        <v>4.225292796731814</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.1073108017066509</v>
+        <v>0.1017750453624334</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>1.494403436229539</v>
+        <v>1.409668558740381</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0.08914631765585825</v>
+        <v>0.07883778238881016</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>0.3536697780701941</v>
+        <v>0.3336262423827134</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>0.02575188751468622</v>
+        <v>0.02222761952383706</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>1.039391631515506</v>
+        <v>1.097733947374646</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>0.06483452065304618</v>
+        <v>0.06089300504698356</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>0.03314017824988575</v>
+        <v>0.0270340738587338</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.07281336747290618</v>
+        <v>0.0666243139780924</v>
       </c>
       <c r="O2" t="n">
         <v>6</v>
@@ -1959,126 +1967,132 @@
         <v>1</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>64.63302219298059</v>
+        <v>1</v>
       </c>
       <c r="R2" s="2" t="n">
-        <v>2.575188751468622</v>
+        <v>66.63737576172866</v>
       </c>
       <c r="S2" s="2" t="n">
-        <v>14.27473646102501</v>
+        <v>2.222761952383706</v>
       </c>
       <c r="T2" s="2" t="n">
+        <v>16.47647655682587</v>
+      </c>
+      <c r="U2" s="2" t="n">
         <v>5.154009202964633</v>
       </c>
-      <c r="U2" s="2" t="n">
-        <v>2.016666231247005</v>
-      </c>
       <c r="V2" s="2" t="n">
-        <v>0.1412751987928607</v>
+        <v>2.129864158455944</v>
       </c>
       <c r="W2" s="2" t="n">
+        <v>0.1292669674314308</v>
+      </c>
+      <c r="X2" s="2" t="n">
         <v>0.2</v>
       </c>
-      <c r="X2" s="2" t="n">
+      <c r="Y2" s="2" t="n">
         <v>0.001154700538379249</v>
       </c>
-      <c r="Y2" s="2" t="n">
-        <v>5.196958157577531</v>
-      </c>
       <c r="Z2" s="2" t="n">
-        <v>0.3653011650747898</v>
+        <v>5.488669736873228</v>
       </c>
       <c r="AA2" s="2" t="n">
-        <v>14.22650310056781</v>
+        <v>0.3346254077456884</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>0.1269824014855127</v>
+        <v>16.40242973135069</v>
       </c>
       <c r="AC2" s="2" t="n">
-        <v>0.2982672399388321</v>
+        <v>0.1204354943652124</v>
       </c>
       <c r="AD2" s="2" t="n">
-        <v>0.1657008912494287</v>
+        <v>0.2796323359132595</v>
       </c>
       <c r="AE2" s="2" t="n">
-        <v>0.03000465191244601</v>
+        <v>0.135170369293669</v>
       </c>
       <c r="AF2" s="2" t="n">
-        <v>0.1333755553812354</v>
+        <v>0.03168884950076702</v>
       </c>
       <c r="AG2" s="2" t="n">
-        <v>0.009375146825498681</v>
+        <v>0</v>
       </c>
       <c r="AH2" s="2" t="n">
-        <v>0.4430640045921314</v>
+        <v>0.1262869171929473</v>
       </c>
       <c r="AI2" s="2" t="n">
-        <v>0.03114356363331814</v>
+        <v>0.007699281098066191</v>
       </c>
       <c r="AJ2" s="2" t="n">
-        <v>0.1924202523243197</v>
+        <v>0.4195160582399656</v>
       </c>
       <c r="AK2" s="2" t="n">
-        <v>0.01352547783275285</v>
+        <v>0.02557645819010131</v>
       </c>
       <c r="AL2" s="2" t="n">
+        <v>0.1821935091634203</v>
+      </c>
+      <c r="AM2" s="2" t="n">
+        <v>0.01110771465859023</v>
+      </c>
+      <c r="AN2" s="2" t="n">
         <v>6.37</v>
       </c>
-      <c r="AM2" s="2" t="n">
+      <c r="AO2" s="2" t="n">
         <v>0.005773502691896135</v>
       </c>
-      <c r="AN2" s="2" t="n">
-        <v>0.8158490043292828</v>
-      </c>
-      <c r="AO2" s="2" t="n">
-        <v>0.05735188883641247</v>
-      </c>
       <c r="AP2" s="2" t="n">
-        <v>33.55515585102087</v>
+        <v>0.8616436007650279</v>
       </c>
       <c r="AQ2" s="2" t="n">
-        <v>2.358833016948221</v>
-      </c>
-      <c r="AR2" s="3" t="n">
-        <v>3.80215800500338e+23</v>
-      </c>
-      <c r="AS2" s="3" t="n">
-        <v>2.672810067601905e+22</v>
+        <v>0.05253726591082174</v>
+      </c>
+      <c r="AR2" s="2" t="n">
+        <v>35.43864754174043</v>
+      </c>
+      <c r="AS2" s="2" t="n">
+        <v>2.160811787805567</v>
       </c>
       <c r="AT2" s="3" t="n">
-        <v>2.421974649187153e+24</v>
+        <v>4.015577756084907e+23</v>
       </c>
       <c r="AU2" s="3" t="n">
-        <v>1.702721521876897e+23</v>
-      </c>
-      <c r="AV2" s="2" t="n">
-        <v>72.00105954340778</v>
-      </c>
-      <c r="AW2" s="2" t="n">
-        <v>5.061471842368986</v>
+        <v>2.448430838106403e+22</v>
+      </c>
+      <c r="AV2" s="3" t="n">
+        <v>2.557923030626086e+24</v>
+      </c>
+      <c r="AW2" s="3" t="n">
+        <v>1.559822747162696e+23</v>
       </c>
       <c r="AX2" s="2" t="n">
+        <v>76.04256654683559</v>
+      </c>
+      <c r="AY2" s="2" t="n">
+        <v>4.636567294952758</v>
+      </c>
+      <c r="AZ2" s="2" t="n">
         <v>2.145752499648045</v>
       </c>
-      <c r="AY2" s="2" t="n">
+      <c r="BA2" s="2" t="n">
         <v>0.8091066252691731</v>
       </c>
-      <c r="AZ2" s="2" t="n">
+      <c r="BB2" s="2" t="n">
         <v>0.1344869893055761</v>
       </c>
-      <c r="BA2" s="2" t="n">
+      <c r="BC2" s="2" t="n">
         <v>33.2778476984484</v>
       </c>
-      <c r="BB2" s="3" t="n">
+      <c r="BD2" s="3" t="n">
         <v>3.770736025715389e+23</v>
       </c>
-      <c r="BC2" s="2" t="n">
-        <v>0.8333115623502168</v>
-      </c>
-      <c r="BD2" s="2" t="n">
-        <v>7.08829801230866</v>
-      </c>
-      <c r="BE2" t="inlineStr"/>
+      <c r="BE2" s="2" t="n">
+        <v>6.493207922797173</v>
+      </c>
+      <c r="BF2" s="2" t="n">
+        <v>6.493243816084644</v>
+      </c>
+      <c r="BG2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2100,34 +2114,34 @@
         <v>295.4176231113203</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>2.638004598960852</v>
+        <v>2.657257238030654</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.1471643758856326</v>
+        <v>0.1479273677345447</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>2.295178778117416</v>
+        <v>2.295164291240656</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.1473935899490647</v>
+        <v>0.1473934774904395</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>0.8700435090300904</v>
+        <v>0.863734326655423</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>0.09018530043733011</v>
+        <v>0.08622567476627345</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0.1392120582045707</v>
+        <v>0.1464900497604954</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>0.08506560731668297</v>
+        <v>0.08498915868226771</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>0.05923196415926527</v>
+        <v>0.05237039653365842</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.1036560809905555</v>
+        <v>0.09982893131057902</v>
       </c>
       <c r="O3" t="n">
         <v>7</v>
@@ -2136,126 +2150,132 @@
         <v>1</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>12.99564909699096</v>
+        <v>1</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>9.018530043733012</v>
+        <v>13.62656733445769</v>
       </c>
       <c r="S3" s="2" t="n">
-        <v>1.343018729574148</v>
+        <v>8.622567476627346</v>
       </c>
       <c r="T3" s="2" t="n">
+        <v>1.467410777991286</v>
+      </c>
+      <c r="U3" s="2" t="n">
         <v>0.9312121114180388</v>
       </c>
-      <c r="U3" s="2" t="n">
-        <v>1.49495540809258</v>
-      </c>
       <c r="V3" s="2" t="n">
-        <v>1.113130721986736</v>
+        <v>1.573111517390191</v>
       </c>
       <c r="W3" s="2" t="n">
+        <v>1.072032140545946</v>
+      </c>
+      <c r="X3" s="2" t="n">
         <v>0.2</v>
       </c>
-      <c r="X3" s="2" t="n">
+      <c r="Y3" s="2" t="n">
         <v>0.001154700538379249</v>
       </c>
-      <c r="Y3" s="2" t="n">
-        <v>0.6960602910228537</v>
-      </c>
       <c r="Z3" s="2" t="n">
-        <v>0.5182959850853944</v>
+        <v>0.7324502488024771</v>
       </c>
       <c r="AA3" s="2" t="n">
-        <v>1.342978358028706</v>
+        <v>0.4991625696546232</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>0.2789312345088457</v>
+        <v>1.467358118036111</v>
       </c>
       <c r="AC3" s="2" t="n">
-        <v>0.3210939194679245</v>
+        <v>0.2783459681987293</v>
       </c>
       <c r="AD3" s="2" t="n">
-        <v>0.2961598207963263</v>
+        <v>0.3210957011943698</v>
       </c>
       <c r="AE3" s="2" t="n">
-        <v>0.004018705963942527</v>
+        <v>0.2618519826682921</v>
       </c>
       <c r="AF3" s="2" t="n">
-        <v>0.9958148589993151</v>
+        <v>0.004228803483141174</v>
       </c>
       <c r="AG3" s="2" t="n">
-        <v>0.7414973242465532</v>
+        <v>0</v>
       </c>
       <c r="AH3" s="2" t="n">
-        <v>3.308025357416123</v>
+        <v>0.9463402895871896</v>
       </c>
       <c r="AI3" s="2" t="n">
-        <v>2.46320079369843</v>
+        <v>0.6449279681321126</v>
       </c>
       <c r="AJ3" s="2" t="n">
-        <v>1.436657158721854</v>
+        <v>3.143674395303528</v>
       </c>
       <c r="AK3" s="2" t="n">
-        <v>1.069754512522938</v>
+        <v>2.142404336516686</v>
       </c>
       <c r="AL3" s="2" t="n">
+        <v>1.365280442780864</v>
+      </c>
+      <c r="AM3" s="2" t="n">
+        <v>0.9304343813547942</v>
+      </c>
+      <c r="AN3" s="2" t="n">
         <v>6.37</v>
       </c>
-      <c r="AM3" s="2" t="n">
+      <c r="AO3" s="2" t="n">
         <v>0.005773502691896135</v>
       </c>
-      <c r="AN3" s="2" t="n">
-        <v>0.1092716312437761</v>
-      </c>
-      <c r="AO3" s="2" t="n">
-        <v>0.08136520707143691</v>
-      </c>
       <c r="AP3" s="2" t="n">
-        <v>22.53191120265777</v>
+        <v>0.1149843404713465</v>
       </c>
       <c r="AQ3" s="2" t="n">
-        <v>16.77758078516743</v>
-      </c>
-      <c r="AR3" s="3" t="n">
-        <v>2.553106501056654e+23</v>
-      </c>
-      <c r="AS3" s="3" t="n">
-        <v>1.90107932653141e+23</v>
+        <v>0.07836154020519386</v>
+      </c>
+      <c r="AR3" s="2" t="n">
+        <v>23.70987711729723</v>
+      </c>
+      <c r="AS3" s="2" t="n">
+        <v>16.15822190544531</v>
       </c>
       <c r="AT3" s="3" t="n">
-        <v>1.626328841173089e+24</v>
+        <v>2.686582636642275e+23</v>
       </c>
       <c r="AU3" s="3" t="n">
-        <v>1.210988428112744e+24</v>
-      </c>
-      <c r="AV3" s="2" t="n">
-        <v>9.643540882980556</v>
-      </c>
-      <c r="AW3" s="2" t="n">
-        <v>7.180717372975728</v>
+        <v>1.830899341882829e+23</v>
+      </c>
+      <c r="AV3" s="3" t="n">
+        <v>1.711353139541129e+24</v>
+      </c>
+      <c r="AW3" s="3" t="n">
+        <v>1.16628391222196e+24</v>
       </c>
       <c r="AX3" s="2" t="n">
+        <v>10.14770417185608</v>
+      </c>
+      <c r="AY3" s="2" t="n">
+        <v>6.915634991631497</v>
+      </c>
+      <c r="AZ3" s="2" t="n">
         <v>0.4279948024046465</v>
       </c>
-      <c r="AY3" s="2" t="n">
+      <c r="BA3" s="2" t="n">
         <v>0.1461871446496136</v>
       </c>
-      <c r="AZ3" s="2" t="n">
+      <c r="BB3" s="2" t="n">
         <v>0.7443494044599881</v>
       </c>
-      <c r="BA3" s="2" t="n">
+      <c r="BC3" s="2" t="n">
         <v>30.14392413404001</v>
       </c>
-      <c r="BB3" s="3" t="n">
+      <c r="BD3" s="3" t="n">
         <v>3.415628970919171e+23</v>
       </c>
-      <c r="BC3" s="2" t="n">
-        <v>-25.25222959537099</v>
-      </c>
-      <c r="BD3" s="2" t="n">
-        <v>55.65825043402813</v>
-      </c>
-      <c r="BE3" t="inlineStr">
+      <c r="BE3" s="2" t="n">
+        <v>-21.34442413049048</v>
+      </c>
+      <c r="BF3" s="2" t="n">
+        <v>53.60357806632963</v>
+      </c>
+      <c r="BG3" t="inlineStr">
         <is>
           <t>LAC &lt; 3σ: HVL/TVL/MFP güvenilir değil</t>
         </is>
@@ -2281,34 +2301,34 @@
         <v>359.5183270178899</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>6.778128508863822</v>
+        <v>6.801409761159016</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.1680365148567579</v>
+        <v>0.169700911156769</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>5.995920649457767</v>
+        <v>5.995887367154187</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.1759015645709348</v>
+        <v>0.1759004160324189</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>0.8845982547567292</v>
+        <v>0.8815653780184004</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.03657660951493821</v>
+        <v>0.03645592105708186</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0.122621686467866</v>
+        <v>0.1260561131123555</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>0.03840892230736111</v>
+        <v>0.038512271395664</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0.01531124780969072</v>
+        <v>0.01506409543499459</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.04134827230130252</v>
+        <v>0.0413536215986932</v>
       </c>
       <c r="O4" t="n">
         <v>7</v>
@@ -2317,130 +2337,132 @@
         <v>1</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>11.54017452432709</v>
+        <v>1</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>3.657660951493821</v>
+        <v>11.84346219815996</v>
       </c>
       <c r="S4" s="2" t="n">
-        <v>2.965581864565676</v>
+        <v>3.645592105708186</v>
       </c>
       <c r="T4" s="2" t="n">
+        <v>3.048248454165353</v>
+      </c>
+      <c r="U4" s="2" t="n">
         <v>0.7726660408861314</v>
       </c>
-      <c r="U4" s="2" t="n">
-        <v>1.586994639071201</v>
-      </c>
       <c r="V4" s="2" t="n">
-        <v>0.5351376935614031</v>
+        <v>1.631443682548649</v>
       </c>
       <c r="W4" s="2" t="n">
+        <v>0.5352069252489321</v>
+      </c>
+      <c r="X4" s="2" t="n">
         <v>0.2</v>
       </c>
-      <c r="X4" s="2" t="n">
+      <c r="Y4" s="2" t="n">
         <v>0.001154700538379249</v>
       </c>
-      <c r="Y4" s="2" t="n">
-        <v>0.61310843233933</v>
-      </c>
       <c r="Z4" s="2" t="n">
-        <v>0.206771663006709</v>
+        <v>0.6302805655617775</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>2.965147271265293</v>
+        <v>0.2068001263770772</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>0.1239549490962107</v>
+        <v>3.047776500931776</v>
       </c>
       <c r="AC4" s="2" t="n">
-        <v>0.1466843666342067</v>
+        <v>0.1247542179607265</v>
       </c>
       <c r="AD4" s="2" t="n">
-        <v>0.07655623904845361</v>
+        <v>0.1466842230859867</v>
       </c>
       <c r="AE4" s="2" t="n">
-        <v>0.003539783184535407</v>
+        <v>0.07532047717497292</v>
       </c>
       <c r="AF4" s="2" t="n">
-        <v>1.130545828435642</v>
+        <v>0.003638926541920808</v>
       </c>
       <c r="AG4" s="2" t="n">
-        <v>0.3812781373092518</v>
+        <v>0</v>
       </c>
       <c r="AH4" s="2" t="n">
-        <v>3.755591950038066</v>
+        <v>1.099743857629711</v>
       </c>
       <c r="AI4" s="2" t="n">
-        <v>1.266578556293925</v>
+        <v>0.3608348109822009</v>
       </c>
       <c r="AJ4" s="2" t="n">
-        <v>1.631032860181805</v>
+        <v>3.653270017839946</v>
       </c>
       <c r="AK4" s="2" t="n">
-        <v>0.5500680778954388</v>
+        <v>1.198667296215145</v>
       </c>
       <c r="AL4" s="2" t="n">
+        <v>1.586595009650483</v>
+      </c>
+      <c r="AM4" s="2" t="n">
+        <v>0.5205745923841277</v>
+      </c>
+      <c r="AN4" s="2" t="n">
         <v>6.37</v>
       </c>
-      <c r="AM4" s="2" t="n">
+      <c r="AO4" s="2" t="n">
         <v>0.005773502691896135</v>
       </c>
-      <c r="AN4" s="2" t="n">
-        <v>0.09624936143474568</v>
-      </c>
-      <c r="AO4" s="2" t="n">
-        <v>0.03246034689448935</v>
-      </c>
       <c r="AP4" s="2" t="n">
-        <v>22.69404562087823</v>
+        <v>0.09894514373026334</v>
       </c>
       <c r="AQ4" s="2" t="n">
-        <v>7.653625772805842</v>
-      </c>
-      <c r="AR4" s="3" t="n">
-        <v>2.571478064546343e+23</v>
-      </c>
-      <c r="AS4" s="3" t="n">
-        <v>8.672376498137641e+22</v>
+        <v>0.03246482188282313</v>
+      </c>
+      <c r="AR4" s="2" t="n">
+        <v>23.32966756669146</v>
+      </c>
+      <c r="AS4" s="2" t="n">
+        <v>7.654680902812794</v>
       </c>
       <c r="AT4" s="3" t="n">
-        <v>1.638031527116021e+24</v>
+        <v>2.643500828504272e+23</v>
       </c>
       <c r="AU4" s="3" t="n">
-        <v>5.524323778999349e+23</v>
-      </c>
-      <c r="AV4" s="2" t="n">
-        <v>8.494287505290718</v>
-      </c>
-      <c r="AW4" s="2" t="n">
-        <v>2.864720502381708</v>
+        <v>8.673572073273714e+22</v>
+      </c>
+      <c r="AV4" s="3" t="n">
+        <v>1.683910027757222e+24</v>
+      </c>
+      <c r="AW4" s="3" t="n">
+        <v>5.525086490616738e+23</v>
       </c>
       <c r="AX4" s="2" t="n">
+        <v>8.732198173252128</v>
+      </c>
+      <c r="AY4" s="2" t="n">
+        <v>2.865115433183568</v>
+      </c>
+      <c r="AZ4" s="2" t="n">
         <v>0.3742958680525469</v>
       </c>
-      <c r="AY4" s="2" t="n">
+      <c r="BA4" s="2" t="n">
         <v>0.1212976516304759</v>
       </c>
-      <c r="AZ4" s="2" t="n">
+      <c r="BB4" s="2" t="n">
         <v>0.8970850844758363</v>
       </c>
-      <c r="BA4" s="2" t="n">
+      <c r="BC4" s="2" t="n">
         <v>28.60002808095189</v>
       </c>
-      <c r="BB4" s="3" t="n">
+      <c r="BD4" s="3" t="n">
         <v>3.240689037300489e+23</v>
       </c>
-      <c r="BC4" s="2" t="n">
-        <v>-20.65026804643995</v>
-      </c>
-      <c r="BD4" s="2" t="n">
-        <v>26.7609030003131</v>
-      </c>
-      <c r="BE4" t="inlineStr">
-        <is>
-          <t>LAC &lt; 3σ: HVL/TVL/MFP güvenilir değil</t>
-        </is>
-      </c>
+      <c r="BE4" s="2" t="n">
+        <v>-18.42781587256757</v>
+      </c>
+      <c r="BF4" s="2" t="n">
+        <v>26.76459226244936</v>
+      </c>
+      <c r="BG4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2462,34 +2484,34 @@
         <v>661.657</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>5.824251387719959</v>
+        <v>5.860779257023759</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.1389577422050872</v>
+        <v>0.1388706024310145</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>5.239064538612317</v>
+        <v>5.23907443718372</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.1236175263603292</v>
+        <v>0.1236177303258328</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>0.8995258256981372</v>
+        <v>0.8939211335941434</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.03082949172978986</v>
+        <v>0.0310279302504868</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0.1058875148329042</v>
+        <v>0.112137725156227</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0.03355543086765616</v>
+        <v>0.03343932473995194</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0.006976737994220559</v>
+        <v>0.009305377291983722</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.03427304792040026</v>
+        <v>0.03470991912422338</v>
       </c>
       <c r="O5" t="n">
         <v>7</v>
@@ -2498,126 +2520,132 @@
         <v>1</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>10.04741743018628</v>
+        <v>1</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>3.082949172978987</v>
+        <v>10.60788664058566</v>
       </c>
       <c r="S5" s="2" t="n">
-        <v>3.08952723080917</v>
+        <v>3.10279302504868</v>
       </c>
       <c r="T5" s="2" t="n">
+        <v>3.230711219893575</v>
+      </c>
+      <c r="U5" s="2" t="n">
         <v>0.5046963885603317</v>
       </c>
-      <c r="U5" s="2" t="n">
-        <v>2.098043838493731</v>
-      </c>
       <c r="V5" s="2" t="n">
-        <v>0.6790824879521252</v>
+        <v>2.22188483409015</v>
       </c>
       <c r="W5" s="2" t="n">
+        <v>0.6877386070313467</v>
+      </c>
+      <c r="X5" s="2" t="n">
         <v>0.2</v>
       </c>
-      <c r="X5" s="2" t="n">
+      <c r="Y5" s="2" t="n">
         <v>0.001154700538379249</v>
       </c>
-      <c r="Y5" s="2" t="n">
-        <v>0.5294375741645209</v>
-      </c>
       <c r="Z5" s="2" t="n">
-        <v>0.1713924992972248</v>
+        <v>0.5606886257811352</v>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>3.08903584658266</v>
+        <v>0.1735797833795434</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>0.1192923630477817</v>
+        <v>3.230149357630856</v>
       </c>
       <c r="AC5" s="2" t="n">
-        <v>0.1179767165008737</v>
+        <v>0.1184745204868339</v>
       </c>
       <c r="AD5" s="2" t="n">
-        <v>0.03488368997110279</v>
+        <v>0.1179766882566798</v>
       </c>
       <c r="AE5" s="2" t="n">
-        <v>0.003056709259629878</v>
+        <v>0.04652688645991861</v>
       </c>
       <c r="AF5" s="2" t="n">
-        <v>1.309214181962371</v>
+        <v>0.003237137290262989</v>
       </c>
       <c r="AG5" s="2" t="n">
-        <v>0.42382615385015</v>
+        <v>0</v>
       </c>
       <c r="AH5" s="2" t="n">
-        <v>4.349115373285776</v>
+        <v>1.236242628596706</v>
       </c>
       <c r="AI5" s="2" t="n">
-        <v>1.407920007822867</v>
+        <v>0.3827199586533747</v>
       </c>
       <c r="AJ5" s="2" t="n">
-        <v>1.888796807778614</v>
+        <v>4.1067091200328</v>
       </c>
       <c r="AK5" s="2" t="n">
-        <v>0.6114518903586544</v>
+        <v>1.271368183124775</v>
       </c>
       <c r="AL5" s="2" t="n">
+        <v>1.783521109612004</v>
+      </c>
+      <c r="AM5" s="2" t="n">
+        <v>0.5521481863984526</v>
+      </c>
+      <c r="AN5" s="2" t="n">
         <v>6.37</v>
       </c>
-      <c r="AM5" s="2" t="n">
+      <c r="AO5" s="2" t="n">
         <v>0.005773502691896135</v>
       </c>
-      <c r="AN5" s="2" t="n">
-        <v>0.08311421886413201</v>
-      </c>
-      <c r="AO5" s="2" t="n">
-        <v>0.02690630628662187</v>
-      </c>
       <c r="AP5" s="2" t="n">
-        <v>27.48048213288326</v>
+        <v>0.0880201924303195</v>
       </c>
       <c r="AQ5" s="2" t="n">
-        <v>8.896170586408347</v>
-      </c>
-      <c r="AR5" s="3" t="n">
-        <v>3.11383250868482e+23</v>
-      </c>
-      <c r="AS5" s="3" t="n">
-        <v>1.008031265274515e+23</v>
+        <v>0.02724969031042304</v>
+      </c>
+      <c r="AR5" s="2" t="n">
+        <v>29.1025694336182</v>
+      </c>
+      <c r="AS5" s="2" t="n">
+        <v>9.00970541426026</v>
       </c>
       <c r="AT5" s="3" t="n">
-        <v>1.983511308032231e+24</v>
+        <v>3.297632346858304e+23</v>
       </c>
       <c r="AU5" s="3" t="n">
-        <v>6.421184326422654e+23</v>
-      </c>
-      <c r="AV5" s="2" t="n">
-        <v>7.33507277643852</v>
-      </c>
-      <c r="AW5" s="2" t="n">
-        <v>2.374560183019267</v>
+        <v>1.020895975439486e+23</v>
+      </c>
+      <c r="AV5" s="3" t="n">
+        <v>2.10059180494874e+24</v>
+      </c>
+      <c r="AW5" s="3" t="n">
+        <v>6.503135233189855e+23</v>
       </c>
       <c r="AX5" s="2" t="n">
+        <v>7.768039284926017</v>
+      </c>
+      <c r="AY5" s="2" t="n">
+        <v>2.404864826908964</v>
+      </c>
+      <c r="AZ5" s="2" t="n">
         <v>0.2669193626578095</v>
       </c>
-      <c r="AY5" s="2" t="n">
+      <c r="BA5" s="2" t="n">
         <v>0.07923020228576637</v>
       </c>
-      <c r="AZ5" s="2" t="n">
+      <c r="BB5" s="2" t="n">
         <v>1.373394373867381</v>
       </c>
-      <c r="BA5" s="2" t="n">
+      <c r="BC5" s="2" t="n">
         <v>26.19628973302349</v>
       </c>
-      <c r="BB5" s="3" t="n">
+      <c r="BD5" s="3" t="n">
         <v>2.9683197763116e+23</v>
       </c>
-      <c r="BC5" s="2" t="n">
-        <v>4.902191924686525</v>
-      </c>
-      <c r="BD5" s="2" t="n">
-        <v>33.95965870385714</v>
-      </c>
-      <c r="BE5" t="inlineStr"/>
+      <c r="BE5" s="2" t="n">
+        <v>11.09424170450748</v>
+      </c>
+      <c r="BF5" s="2" t="n">
+        <v>34.393059116698</v>
+      </c>
+      <c r="BG5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2639,34 +2667,34 @@
         <v>1173.228</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>20.46095516938237</v>
+        <v>20.39164525436896</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.2342864393463963</v>
+        <v>0.2327040117564478</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>19.05462213598214</v>
+        <v>19.0545984070455</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.2440810705777872</v>
+        <v>0.2440804871145263</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>0.9312674788758323</v>
+        <v>0.9344316345912793</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.02904294055376019</v>
+        <v>0.029429833718739</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0.07120874020186956</v>
+        <v>0.06781681196833199</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>0.01718128345025596</v>
+        <v>0.01715551688639427</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.02602689172215715</v>
+        <v>0.02641244322607389</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.03118646491212064</v>
+        <v>0.03149490302906068</v>
       </c>
       <c r="O6" t="n">
         <v>8</v>
@@ -2675,126 +2703,132 @@
         <v>1</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>6.873252112416772</v>
+        <v>1</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>2.904294055376019</v>
+        <v>6.556836540872069</v>
       </c>
       <c r="S6" s="2" t="n">
-        <v>2.283321960425025</v>
+        <v>2.9429833718739</v>
       </c>
       <c r="T6" s="2" t="n">
+        <v>2.153263082148775</v>
+      </c>
+      <c r="U6" s="2" t="n">
         <v>0.3649451484627882</v>
       </c>
-      <c r="U6" s="2" t="n">
-        <v>1.951217614532294</v>
-      </c>
       <c r="V6" s="2" t="n">
-        <v>0.8545521167628449</v>
+        <v>1.858274106505815</v>
       </c>
       <c r="W6" s="2" t="n">
+        <v>0.8630037462265939</v>
+      </c>
+      <c r="X6" s="2" t="n">
         <v>0.2</v>
       </c>
-      <c r="X6" s="2" t="n">
+      <c r="Y6" s="2" t="n">
         <v>0.001154700538379249</v>
       </c>
-      <c r="Y6" s="2" t="n">
-        <v>0.3560437010093477</v>
-      </c>
       <c r="Z6" s="2" t="n">
-        <v>0.1559458733453403</v>
+        <v>0.3390840598416599</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>2.28312358237844</v>
+        <v>0.1574866836282875</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>0.05725207777615897</v>
+        <v>2.153096706525313</v>
       </c>
       <c r="AC6" s="2" t="n">
-        <v>0.06404773310011544</v>
+        <v>0.0570586651674392</v>
       </c>
       <c r="AD6" s="2" t="n">
-        <v>0.1301344586107858</v>
+        <v>0.0640476597565753</v>
       </c>
       <c r="AE6" s="2" t="n">
-        <v>0.00205561926621017</v>
+        <v>0.1320622161303694</v>
       </c>
       <c r="AF6" s="2" t="n">
-        <v>1.946803660884727</v>
+        <v>0.00195770273227493</v>
       </c>
       <c r="AG6" s="2" t="n">
-        <v>0.8526930718558159</v>
+        <v>0</v>
       </c>
       <c r="AH6" s="2" t="n">
-        <v>6.467141776322544</v>
+        <v>2.044175066452903</v>
       </c>
       <c r="AI6" s="2" t="n">
-        <v>2.832585071713644</v>
+        <v>0.9494116359277754</v>
       </c>
       <c r="AJ6" s="2" t="n">
-        <v>2.808643987142875</v>
+        <v>6.79060258411814</v>
       </c>
       <c r="AK6" s="2" t="n">
-        <v>1.230176066166762</v>
+        <v>3.153877187001449</v>
       </c>
       <c r="AL6" s="2" t="n">
+        <v>2.949121231080471</v>
+      </c>
+      <c r="AM6" s="2" t="n">
+        <v>1.36971145891528</v>
+      </c>
+      <c r="AN6" s="2" t="n">
         <v>6.37</v>
       </c>
-      <c r="AM6" s="2" t="n">
+      <c r="AO6" s="2" t="n">
         <v>0.005773502691896135</v>
       </c>
-      <c r="AN6" s="2" t="n">
-        <v>0.05589383061371236</v>
-      </c>
-      <c r="AO6" s="2" t="n">
-        <v>0.02448135121418641</v>
-      </c>
       <c r="AP6" s="2" t="n">
-        <v>24.85613882669739</v>
+        <v>0.05323140656854943</v>
       </c>
       <c r="AQ6" s="2" t="n">
-        <v>10.88692361506654</v>
-      </c>
-      <c r="AR6" s="3" t="n">
-        <v>2.816466346721723e+23</v>
-      </c>
-      <c r="AS6" s="3" t="n">
-        <v>1.233604873023596e+23</v>
+        <v>0.02472323131921058</v>
+      </c>
+      <c r="AR6" s="2" t="n">
+        <v>23.67215159670296</v>
+      </c>
+      <c r="AS6" s="2" t="n">
+        <v>10.99448835707622</v>
       </c>
       <c r="AT6" s="3" t="n">
-        <v>1.794089062861738e+24</v>
+        <v>2.682307931712957e+23</v>
       </c>
       <c r="AU6" s="3" t="n">
-        <v>7.85807986565032e+23</v>
-      </c>
-      <c r="AV6" s="2" t="n">
-        <v>4.93279394198141</v>
-      </c>
-      <c r="AW6" s="2" t="n">
-        <v>2.160550809184148</v>
+        <v>1.245793108617078e+23</v>
+      </c>
+      <c r="AV6" s="3" t="n">
+        <v>1.708630152501154e+24</v>
+      </c>
+      <c r="AW6" s="3" t="n">
+        <v>7.935717212439919e+23</v>
       </c>
       <c r="AX6" s="2" t="n">
+        <v>4.697827237127523</v>
+      </c>
+      <c r="AY6" s="2" t="n">
+        <v>2.18189743552284</v>
+      </c>
+      <c r="AZ6" s="2" t="n">
         <v>0.1984537492477799</v>
       </c>
-      <c r="AY6" s="2" t="n">
+      <c r="BA6" s="2" t="n">
         <v>0.05729123209776895</v>
       </c>
-      <c r="AZ6" s="2" t="n">
+      <c r="BB6" s="2" t="n">
         <v>1.899318797577117</v>
       </c>
-      <c r="BA6" s="2" t="n">
+      <c r="BC6" s="2" t="n">
         <v>25.47756707562872</v>
       </c>
-      <c r="BB6" s="3" t="n">
+      <c r="BD6" s="3" t="n">
         <v>2.88688081303205e+23</v>
       </c>
-      <c r="BC6" s="2" t="n">
-        <v>-2.439119273385309</v>
-      </c>
-      <c r="BD6" s="2" t="n">
-        <v>42.73140988207123</v>
-      </c>
-      <c r="BE6" t="inlineStr">
+      <c r="BE6" s="2" t="n">
+        <v>-7.086294674709252</v>
+      </c>
+      <c r="BF6" s="2" t="n">
+        <v>43.1536038132672</v>
+      </c>
+      <c r="BG6" t="inlineStr">
         <is>
           <t>LAC &lt; 3σ: HVL/TVL/MFP güvenilir değil</t>
         </is>
@@ -2820,34 +2854,34 @@
         <v>1332.492</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>20.43446032046705</v>
+        <v>20.36980996721254</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.1632592034204253</v>
+        <v>0.162247758584232</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>19.08342353301305</v>
+        <v>19.08341053184378</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.1698018719579462</v>
+        <v>0.1698015148540204</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>0.9338843910597039</v>
+        <v>0.9368477449009412</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.01417664979245994</v>
+        <v>0.01425876183993261</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0.06840262672312966</v>
+        <v>0.06523450204843681</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>0.01195837565675302</v>
+        <v>0.01194214700467852</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0.009350877410202204</v>
+        <v>0.009435653034942549</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.01518030489445627</v>
+        <v>0.01521993506152942</v>
       </c>
       <c r="O7" t="n">
         <v>8</v>
@@ -2856,126 +2890,132 @@
         <v>1</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>6.611560894029611</v>
+        <v>1</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>1.417664979245994</v>
+        <v>6.315225509905876</v>
       </c>
       <c r="S7" s="2" t="n">
-        <v>4.506011387696815</v>
+        <v>1.425876183993261</v>
       </c>
       <c r="T7" s="2" t="n">
+        <v>4.286122232763424</v>
+      </c>
+      <c r="U7" s="2" t="n">
         <v>0.341118237048898</v>
       </c>
-      <c r="U7" s="2" t="n">
-        <v>2.005246840945781</v>
-      </c>
       <c r="V7" s="2" t="n">
-        <v>0.4450159283709078</v>
+        <v>1.91237216200451</v>
       </c>
       <c r="W7" s="2" t="n">
+        <v>0.4461777005299105</v>
+      </c>
+      <c r="X7" s="2" t="n">
         <v>0.2</v>
       </c>
-      <c r="X7" s="2" t="n">
+      <c r="Y7" s="2" t="n">
         <v>0.001154700538379249</v>
       </c>
-      <c r="Y7" s="2" t="n">
-        <v>0.3420131336156483</v>
-      </c>
       <c r="Z7" s="2" t="n">
-        <v>0.07592720537902414</v>
+        <v>0.326172510242184</v>
       </c>
       <c r="AA7" s="2" t="n">
-        <v>4.504487316612521</v>
+        <v>0.07612297199582552</v>
       </c>
       <c r="AB7" s="2" t="n">
-        <v>0.0399470308635716</v>
+        <v>4.284810507136675</v>
       </c>
       <c r="AC7" s="2" t="n">
-        <v>0.04448936315441521</v>
+        <v>0.039825545462964</v>
       </c>
       <c r="AD7" s="2" t="n">
-        <v>0.04675438705101102</v>
+        <v>0.04448929990021409</v>
       </c>
       <c r="AE7" s="2" t="n">
-        <v>0.001974613747593815</v>
+        <v>0.04717826517471274</v>
       </c>
       <c r="AF7" s="2" t="n">
-        <v>2.026668313091446</v>
+        <v>0.001883157865905804</v>
       </c>
       <c r="AG7" s="2" t="n">
-        <v>0.4499220822793985</v>
+        <v>0</v>
       </c>
       <c r="AH7" s="2" t="n">
-        <v>6.732446408276453</v>
+        <v>2.125093804028063</v>
       </c>
       <c r="AI7" s="2" t="n">
-        <v>1.494608805634158</v>
+        <v>0.4959598097718813</v>
       </c>
       <c r="AJ7" s="2" t="n">
-        <v>2.923864324823831</v>
+        <v>7.059408811871883</v>
       </c>
       <c r="AK7" s="2" t="n">
-        <v>0.6491003568909245</v>
+        <v>1.647542826016204</v>
       </c>
       <c r="AL7" s="2" t="n">
+        <v>3.06586229249515</v>
+      </c>
+      <c r="AM7" s="2" t="n">
+        <v>0.7155187580381267</v>
+      </c>
+      <c r="AN7" s="2" t="n">
         <v>6.37</v>
       </c>
-      <c r="AM7" s="2" t="n">
+      <c r="AO7" s="2" t="n">
         <v>0.005773502691896135</v>
       </c>
-      <c r="AN7" s="2" t="n">
-        <v>0.05369122976697775</v>
-      </c>
-      <c r="AO7" s="2" t="n">
-        <v>0.01191959782795906</v>
-      </c>
       <c r="AP7" s="2" t="n">
-        <v>25.48482990062792</v>
+        <v>0.05120447570520942</v>
       </c>
       <c r="AQ7" s="2" t="n">
-        <v>5.657700977381238</v>
-      </c>
-      <c r="AR7" s="3" t="n">
-        <v>2.887703768774895e+23</v>
-      </c>
-      <c r="AS7" s="3" t="n">
-        <v>6.410780255819037e+22</v>
+        <v>0.01195032119976833</v>
+      </c>
+      <c r="AR7" s="2" t="n">
+        <v>24.30447876052721</v>
+      </c>
+      <c r="AS7" s="2" t="n">
+        <v>5.672283990434415</v>
       </c>
       <c r="AT7" s="3" t="n">
-        <v>1.839467300709608e+24</v>
+        <v>2.753957361636326e+23</v>
       </c>
       <c r="AU7" s="3" t="n">
-        <v>4.083701056087006e+23</v>
-      </c>
-      <c r="AV7" s="2" t="n">
-        <v>4.738407978556136</v>
-      </c>
-      <c r="AW7" s="2" t="n">
-        <v>1.051939352000445</v>
+        <v>6.427304369151539e+22</v>
+      </c>
+      <c r="AV7" s="3" t="n">
+        <v>1.754270839362339e+24</v>
+      </c>
+      <c r="AW7" s="3" t="n">
+        <v>4.094223757173503e+23</v>
       </c>
       <c r="AX7" s="2" t="n">
+        <v>4.518944663259956</v>
+      </c>
+      <c r="AY7" s="2" t="n">
+        <v>1.054650779373985</v>
+      </c>
+      <c r="AZ7" s="2" t="n">
         <v>0.1859305318902437</v>
       </c>
-      <c r="AY7" s="2" t="n">
+      <c r="BA7" s="2" t="n">
         <v>0.05355074364974851</v>
       </c>
-      <c r="AZ7" s="2" t="n">
+      <c r="BB7" s="2" t="n">
         <v>2.031985116235768</v>
       </c>
-      <c r="BA7" s="2" t="n">
+      <c r="BC7" s="2" t="n">
         <v>25.41814741232349</v>
       </c>
-      <c r="BB7" s="3" t="n">
+      <c r="BD7" s="3" t="n">
         <v>2.880147929731086e+23</v>
       </c>
-      <c r="BC7" s="2" t="n">
-        <v>0.2623420472890149</v>
-      </c>
-      <c r="BD7" s="2" t="n">
-        <v>22.25851036900594</v>
-      </c>
-      <c r="BE7" t="inlineStr"/>
+      <c r="BE7" s="2" t="n">
+        <v>-4.381391899774493</v>
+      </c>
+      <c r="BF7" s="2" t="n">
+        <v>22.31588281561511</v>
+      </c>
+      <c r="BG7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2997,34 +3037,34 @@
         <v>80.89906428571429</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>4.225420233483845</v>
+        <v>4.225292796731814</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.1073108017066509</v>
+        <v>0.1017750453624334</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.3798037375682231</v>
+        <v>0.3910142797341428</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.0439357835983932</v>
+        <v>0.04610134433189879</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>0.08988543543160819</v>
+        <v>0.09254134530903636</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.01166213367276159</v>
+        <v>0.01203434246183361</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>2.409219359176548</v>
+        <v>2.380099758014007</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>0.1184352006467461</v>
+        <v>0.1203372639903481</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0.05297846476803805</v>
+        <v>0.0492959617440567</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.1297444198469177</v>
+        <v>0.1300428735031422</v>
       </c>
       <c r="O8" t="n">
         <v>6</v>
@@ -3033,126 +3073,132 @@
         <v>1</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>91.01145645683918</v>
+        <v>1</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>1.166213367276159</v>
+        <v>90.74586546909636</v>
       </c>
       <c r="S8" s="2" t="n">
-        <v>18.56896321259232</v>
+        <v>1.203434246183361</v>
       </c>
       <c r="T8" s="2" t="n">
+        <v>18.30242360767657</v>
+      </c>
+      <c r="U8" s="2" t="n">
         <v>10.60366823249836</v>
       </c>
-      <c r="U8" s="2" t="n">
-        <v>2.272062182964871</v>
-      </c>
       <c r="V8" s="2" t="n">
-        <v>0.1223580528946333</v>
+        <v>2.244600364541228</v>
       </c>
       <c r="W8" s="2" t="n">
+        <v>0.1226395155448035</v>
+      </c>
+      <c r="X8" s="2" t="n">
         <v>0.2</v>
       </c>
-      <c r="X8" s="2" t="n">
+      <c r="Y8" s="2" t="n">
         <v>0.001154700538379249</v>
       </c>
-      <c r="Y8" s="2" t="n">
-        <v>12.04609679588274</v>
-      </c>
       <c r="Z8" s="2" t="n">
-        <v>0.6524395070062234</v>
+        <v>11.90049879007003</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>18.4631627400329</v>
+        <v>0.6538344230554637</v>
       </c>
       <c r="AB8" s="2" t="n">
-        <v>0.1269824014855127</v>
+        <v>18.20108940495556</v>
       </c>
       <c r="AC8" s="2" t="n">
-        <v>0.5784011484418468</v>
+        <v>0.1204354943652124</v>
       </c>
       <c r="AD8" s="2" t="n">
-        <v>0.2648923238401902</v>
+        <v>0.5895097279214951</v>
       </c>
       <c r="AE8" s="2" t="n">
-        <v>0.0695481722778717</v>
+        <v>0.2464798087202835</v>
       </c>
       <c r="AF8" s="2" t="n">
-        <v>0.05754122620007979</v>
+        <v>0.06870756179937731</v>
       </c>
       <c r="AG8" s="2" t="n">
-        <v>0.003116542220326941</v>
+        <v>0</v>
       </c>
       <c r="AH8" s="2" t="n">
-        <v>0.1911478159283139</v>
+        <v>0.05824522087581055</v>
       </c>
       <c r="AI8" s="2" t="n">
-        <v>0.01035292916060671</v>
+        <v>0.003200095311874699</v>
       </c>
       <c r="AJ8" s="2" t="n">
-        <v>0.08301444168552521</v>
+        <v>0.193486435620275</v>
       </c>
       <c r="AK8" s="2" t="n">
-        <v>0.004496220005986757</v>
+        <v>0.0106304865228339</v>
       </c>
       <c r="AL8" s="2" t="n">
+        <v>0.08403009131301421</v>
+      </c>
+      <c r="AM8" s="2" t="n">
+        <v>0.004616761636813649</v>
+      </c>
+      <c r="AN8" s="2" t="n">
         <v>6.28</v>
       </c>
-      <c r="AM8" s="2" t="n">
+      <c r="AO8" s="2" t="n">
         <v>0.005773502691896135</v>
       </c>
-      <c r="AN8" s="2" t="n">
-        <v>1.918168279599163</v>
-      </c>
-      <c r="AO8" s="2" t="n">
-        <v>0.1039066067345771</v>
-      </c>
       <c r="AP8" s="2" t="n">
-        <v>54.51585293094176</v>
+        <v>1.894983883769114</v>
       </c>
       <c r="AQ8" s="2" t="n">
-        <v>2.953107582656471</v>
-      </c>
-      <c r="AR8" s="3" t="n">
-        <v>5.938386972012958e+23</v>
-      </c>
-      <c r="AS8" s="3" t="n">
-        <v>3.216806608164889e+22</v>
+        <v>0.1041283364117177</v>
+      </c>
+      <c r="AR8" s="2" t="n">
+        <v>53.85693414534501</v>
+      </c>
+      <c r="AS8" s="2" t="n">
+        <v>2.95940931467758</v>
       </c>
       <c r="AT8" s="3" t="n">
-        <v>3.729307018424138e+24</v>
+        <v>5.866611249509651e+23</v>
       </c>
       <c r="AU8" s="3" t="n">
-        <v>2.020445467445392e+23</v>
-      </c>
-      <c r="AV8" s="2" t="n">
-        <v>176.0925657426108</v>
-      </c>
-      <c r="AW8" s="2" t="n">
-        <v>9.538882053311641</v>
+        <v>3.223671056086611e+22</v>
+      </c>
+      <c r="AV8" s="3" t="n">
+        <v>3.684231864692061e+24</v>
+      </c>
+      <c r="AW8" s="3" t="n">
+        <v>2.02474874673578e+23</v>
       </c>
       <c r="AX8" s="2" t="n">
+        <v>173.9641811841096</v>
+      </c>
+      <c r="AY8" s="2" t="n">
+        <v>9.559237383010418</v>
+      </c>
+      <c r="AZ8" s="2" t="n">
         <v>3.230116677541063</v>
       </c>
-      <c r="AY8" s="2" t="n">
+      <c r="BA8" s="2" t="n">
         <v>1.688482202627127</v>
       </c>
-      <c r="AZ8" s="2" t="n">
+      <c r="BB8" s="2" t="n">
         <v>0.06536862200531438</v>
       </c>
-      <c r="BA8" s="2" t="n">
+      <c r="BC8" s="2" t="n">
         <v>47.9879937615111</v>
       </c>
-      <c r="BB8" s="3" t="n">
+      <c r="BD8" s="3" t="n">
         <v>5.22731025280638e+23</v>
       </c>
-      <c r="BC8" s="2" t="n">
-        <v>13.60310914824357</v>
-      </c>
-      <c r="BD8" s="2" t="n">
-        <v>6.153846725355332</v>
-      </c>
-      <c r="BE8" t="inlineStr"/>
+      <c r="BE8" s="2" t="n">
+        <v>12.23001822706144</v>
+      </c>
+      <c r="BF8" s="2" t="n">
+        <v>6.166978618412639</v>
+      </c>
+      <c r="BG8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -3174,10 +3220,10 @@
         <v>295.4176231113203</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>2.638004598960852</v>
+        <v>2.657257238030654</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.1471643758856326</v>
+        <v>0.1479273677345447</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>1.961510609011513</v>
@@ -3186,22 +3232,22 @@
         <v>0.139767831513998</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>0.7435584493613772</v>
+        <v>0.7381711416337046</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.08859439141877606</v>
+        <v>0.09265339807660357</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0.2963079023703815</v>
+        <v>0.3035795820334734</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>0.09049535306375088</v>
+        <v>0.09042324205229151</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0.07750562547833741</v>
+        <v>0.08705332111633689</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.1191491959977961</v>
+        <v>0.1255175024473932</v>
       </c>
       <c r="O9" t="n">
         <v>7</v>
@@ -3210,126 +3256,132 @@
         <v>1</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>25.64415506386229</v>
+        <v>1</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>8.859439141877607</v>
+        <v>26.18288583662954</v>
       </c>
       <c r="S9" s="2" t="n">
-        <v>2.486864471799392</v>
+        <v>9.265339807660357</v>
       </c>
       <c r="T9" s="2" t="n">
+        <v>2.418623507591775</v>
+      </c>
+      <c r="U9" s="2" t="n">
         <v>1.077177645548336</v>
       </c>
-      <c r="U9" s="2" t="n">
-        <v>2.750780278396386</v>
-      </c>
       <c r="V9" s="2" t="n">
-        <v>1.106123920137085</v>
+        <v>2.818287060524141</v>
       </c>
       <c r="W9" s="2" t="n">
+        <v>1.165244219151046</v>
+      </c>
+      <c r="X9" s="2" t="n">
         <v>0.2</v>
       </c>
-      <c r="X9" s="2" t="n">
+      <c r="Y9" s="2" t="n">
         <v>0.001154700538379249</v>
       </c>
-      <c r="Y9" s="2" t="n">
-        <v>1.481539511851907</v>
-      </c>
       <c r="Z9" s="2" t="n">
-        <v>0.5958073832908334</v>
+        <v>1.517897910167367</v>
       </c>
       <c r="AA9" s="2" t="n">
-        <v>2.486608178080798</v>
+        <v>0.6276486963139815</v>
       </c>
       <c r="AB9" s="2" t="n">
-        <v>0.2789312345088457</v>
+        <v>2.418387736773117</v>
       </c>
       <c r="AC9" s="2" t="n">
+        <v>0.2783459681987293</v>
+      </c>
+      <c r="AD9" s="2" t="n">
         <v>0.3562760019545162</v>
       </c>
-      <c r="AD9" s="2" t="n">
-        <v>0.387528127391687</v>
-      </c>
       <c r="AE9" s="2" t="n">
-        <v>0.008553672359827631</v>
+        <v>0.4352666055816844</v>
       </c>
       <c r="AF9" s="2" t="n">
-        <v>0.4678560207236858</v>
+        <v>0.008763587670374972</v>
       </c>
       <c r="AG9" s="2" t="n">
-        <v>0.1881502782978797</v>
+        <v>0</v>
       </c>
       <c r="AH9" s="2" t="n">
-        <v>1.554184059604216</v>
+        <v>0.4566494069970208</v>
       </c>
       <c r="AI9" s="2" t="n">
-        <v>0.6250216955386027</v>
+        <v>0.1888239011691043</v>
       </c>
       <c r="AJ9" s="2" t="n">
-        <v>0.6749735609481057</v>
+        <v>1.516956494617057</v>
       </c>
       <c r="AK9" s="2" t="n">
-        <v>0.2714434734422294</v>
+        <v>0.6272594222798823</v>
       </c>
       <c r="AL9" s="2" t="n">
+        <v>0.6588058348994879</v>
+      </c>
+      <c r="AM9" s="2" t="n">
+        <v>0.2724153058179745</v>
+      </c>
+      <c r="AN9" s="2" t="n">
         <v>6.28</v>
       </c>
-      <c r="AM9" s="2" t="n">
+      <c r="AO9" s="2" t="n">
         <v>0.005773502691896135</v>
       </c>
-      <c r="AN9" s="2" t="n">
-        <v>0.2359139350082655</v>
-      </c>
-      <c r="AO9" s="2" t="n">
-        <v>0.09487403505582533</v>
-      </c>
       <c r="AP9" s="2" t="n">
-        <v>46.63926122130088</v>
+        <v>0.2417034888801539</v>
       </c>
       <c r="AQ9" s="2" t="n">
-        <v>18.75622524770512</v>
-      </c>
-      <c r="AR9" s="3" t="n">
-        <v>5.080393432929047e+23</v>
-      </c>
-      <c r="AS9" s="3" t="n">
-        <v>2.043107053579552e+23</v>
+        <v>0.09994430694582744</v>
+      </c>
+      <c r="AR9" s="2" t="n">
+        <v>47.78383335255858</v>
+      </c>
+      <c r="AS9" s="2" t="n">
+        <v>19.75859814751938</v>
       </c>
       <c r="AT9" s="3" t="n">
-        <v>3.190487075879441e+24</v>
+        <v>5.205071152663155e+23</v>
       </c>
       <c r="AU9" s="3" t="n">
-        <v>1.283074582327986e+24</v>
-      </c>
-      <c r="AV9" s="2" t="n">
-        <v>21.65747945676702</v>
-      </c>
-      <c r="AW9" s="2" t="n">
-        <v>8.709669757872257</v>
+        <v>2.152295075949782e+23</v>
+      </c>
+      <c r="AV9" s="3" t="n">
+        <v>3.268784683872462e+24</v>
+      </c>
+      <c r="AW9" s="3" t="n">
+        <v>1.351644648416627e+24</v>
       </c>
       <c r="AX9" s="2" t="n">
+        <v>22.18897474143462</v>
+      </c>
+      <c r="AY9" s="2" t="n">
+        <v>9.175133187550953</v>
+      </c>
+      <c r="AZ9" s="2" t="n">
         <v>0.4643615462518457</v>
       </c>
-      <c r="AY9" s="2" t="n">
+      <c r="BA9" s="2" t="n">
         <v>0.171525102794321</v>
       </c>
-      <c r="AZ9" s="2" t="n">
+      <c r="BB9" s="2" t="n">
         <v>0.6434845574678629</v>
       </c>
-      <c r="BA9" s="2" t="n">
+      <c r="BC9" s="2" t="n">
         <v>33.90984120948404</v>
       </c>
-      <c r="BB9" s="3" t="n">
+      <c r="BD9" s="3" t="n">
         <v>3.693783522318075e+23</v>
       </c>
-      <c r="BC9" s="2" t="n">
-        <v>37.53901391981928</v>
-      </c>
-      <c r="BD9" s="2" t="n">
-        <v>55.31204092592242</v>
-      </c>
-      <c r="BE9" t="inlineStr">
+      <c r="BE9" s="2" t="n">
+        <v>40.91435302620702</v>
+      </c>
+      <c r="BF9" s="2" t="n">
+        <v>58.2680350092386</v>
+      </c>
+      <c r="BG9" t="inlineStr">
         <is>
           <t>LAC &lt; 3σ: HVL/TVL/MFP güvenilir değil</t>
         </is>
@@ -3355,10 +3407,10 @@
         <v>359.5183270178899</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>6.778128508863822</v>
+        <v>6.801409761159016</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0.1680365148567579</v>
+        <v>0.169700911156769</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>5.605868404607805</v>
@@ -3367,22 +3419,22 @@
         <v>0.1628243133529456</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>0.827052540723735</v>
+        <v>0.8242215366322112</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.0332282114597998</v>
+        <v>0.03359411841006289</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>0.1898870542670253</v>
+        <v>0.1933159300715522</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>0.0381867062304185</v>
+        <v>0.03829067709600099</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>0.0124875834798939</v>
+        <v>0.0139673822696891</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.04017666329967687</v>
+        <v>0.04075860301749607</v>
       </c>
       <c r="O10" t="n">
         <v>7</v>
@@ -3391,126 +3443,132 @@
         <v>1</v>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>17.2947459276265</v>
+        <v>1</v>
       </c>
       <c r="R10" s="2" t="n">
-        <v>3.32282114597998</v>
+        <v>17.57784633677888</v>
       </c>
       <c r="S10" s="2" t="n">
-        <v>4.72630225289397</v>
+        <v>3.359411841006289</v>
       </c>
       <c r="T10" s="2" t="n">
+        <v>4.7429478873103</v>
+      </c>
+      <c r="U10" s="2" t="n">
         <v>0.8527865423494825</v>
       </c>
-      <c r="U10" s="2" t="n">
-        <v>2.226665699295326</v>
-      </c>
       <c r="V10" s="2" t="n">
-        <v>0.4711221543082463</v>
+        <v>2.266873601674743</v>
       </c>
       <c r="W10" s="2" t="n">
+        <v>0.4779461329819237</v>
+      </c>
+      <c r="X10" s="2" t="n">
         <v>0.2</v>
       </c>
-      <c r="X10" s="2" t="n">
+      <c r="Y10" s="2" t="n">
         <v>0.001154700538379249</v>
       </c>
-      <c r="Y10" s="2" t="n">
-        <v>0.9494352713351265</v>
-      </c>
       <c r="Z10" s="2" t="n">
-        <v>0.2009580912160673</v>
+        <v>0.9665796503577609</v>
       </c>
       <c r="AA10" s="2" t="n">
-        <v>4.724543637878741</v>
+        <v>0.2038694080511562</v>
       </c>
       <c r="AB10" s="2" t="n">
-        <v>0.1239549490962107</v>
+        <v>4.74117063269846</v>
       </c>
       <c r="AC10" s="2" t="n">
+        <v>0.1247542179607265</v>
+      </c>
+      <c r="AD10" s="2" t="n">
         <v>0.1452266639180385</v>
       </c>
-      <c r="AD10" s="2" t="n">
-        <v>0.06243791739946949</v>
-      </c>
       <c r="AE10" s="2" t="n">
-        <v>0.005481567094834592</v>
+        <v>0.06983691134844548</v>
       </c>
       <c r="AF10" s="2" t="n">
-        <v>0.7300625977221379</v>
+        <v>0.005580550213272662</v>
       </c>
       <c r="AG10" s="2" t="n">
-        <v>0.1545255274750572</v>
+        <v>0</v>
       </c>
       <c r="AH10" s="2" t="n">
-        <v>2.425215454399621</v>
+        <v>0.7171133597768069</v>
       </c>
       <c r="AI10" s="2" t="n">
-        <v>0.5133226910966816</v>
+        <v>0.1512523837111212</v>
       </c>
       <c r="AJ10" s="2" t="n">
-        <v>1.053257689272243</v>
+        <v>2.382199017061644</v>
       </c>
       <c r="AK10" s="2" t="n">
-        <v>0.2229332121790162</v>
+        <v>0.5024495428686574</v>
       </c>
       <c r="AL10" s="2" t="n">
+        <v>1.034575887905222</v>
+      </c>
+      <c r="AM10" s="2" t="n">
+        <v>0.2182110639026693</v>
+      </c>
+      <c r="AN10" s="2" t="n">
         <v>6.28</v>
       </c>
-      <c r="AM10" s="2" t="n">
+      <c r="AO10" s="2" t="n">
         <v>0.005773502691896135</v>
       </c>
-      <c r="AN10" s="2" t="n">
-        <v>0.1511839604036826</v>
-      </c>
-      <c r="AO10" s="2" t="n">
-        <v>0.03199999790477622</v>
-      </c>
       <c r="AP10" s="2" t="n">
-        <v>35.02343934375751</v>
+        <v>0.1539139570633377</v>
       </c>
       <c r="AQ10" s="2" t="n">
-        <v>7.413154031854545</v>
-      </c>
-      <c r="AR10" s="3" t="n">
-        <v>3.81508725870104e+23</v>
-      </c>
-      <c r="AS10" s="3" t="n">
-        <v>8.07511484412721e+22</v>
+        <v>0.03246358992020588</v>
+      </c>
+      <c r="AR10" s="2" t="n">
+        <v>35.65587331468134</v>
+      </c>
+      <c r="AS10" s="2" t="n">
+        <v>7.520550258208829</v>
       </c>
       <c r="AT10" s="3" t="n">
-        <v>2.395874798464253e+24</v>
+        <v>3.883978002432959e+23</v>
       </c>
       <c r="AU10" s="3" t="n">
-        <v>5.071219957279627e+23</v>
-      </c>
-      <c r="AV10" s="2" t="n">
-        <v>13.87905939732096</v>
-      </c>
-      <c r="AW10" s="2" t="n">
-        <v>2.937678510661091</v>
+        <v>8.192101063206185e+22</v>
+      </c>
+      <c r="AV10" s="3" t="n">
+        <v>2.439138185527898e+24</v>
+      </c>
+      <c r="AW10" s="3" t="n">
+        <v>5.144688338022717e+23</v>
       </c>
       <c r="AX10" s="2" t="n">
+        <v>14.12967980501944</v>
+      </c>
+      <c r="AY10" s="2" t="n">
+        <v>2.980237397867721</v>
+      </c>
+      <c r="AZ10" s="2" t="n">
         <v>0.3962791678195</v>
       </c>
-      <c r="AY10" s="2" t="n">
+      <c r="BA10" s="2" t="n">
         <v>0.1357940354059685</v>
       </c>
-      <c r="AZ10" s="2" t="n">
+      <c r="BB10" s="2" t="n">
         <v>0.8128026723431629</v>
       </c>
-      <c r="BA10" s="2" t="n">
+      <c r="BC10" s="2" t="n">
         <v>31.45819271823463</v>
       </c>
-      <c r="BB10" s="3" t="n">
+      <c r="BD10" s="3" t="n">
         <v>3.42672657140082e+23</v>
       </c>
-      <c r="BC10" s="2" t="n">
-        <v>11.33328496476627</v>
-      </c>
-      <c r="BD10" s="2" t="n">
-        <v>23.56509828219578</v>
-      </c>
-      <c r="BE10" t="inlineStr"/>
+      <c r="BE10" s="2" t="n">
+        <v>13.34368008373713</v>
+      </c>
+      <c r="BF10" s="2" t="n">
+        <v>23.90649178600006</v>
+      </c>
+      <c r="BG10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -3532,10 +3590,10 @@
         <v>661.657</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>5.824251387719959</v>
+        <v>5.860779257023759</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>0.1389577422050872</v>
+        <v>0.1388706024310145</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>5.308799235059366</v>
@@ -3544,22 +3602,22 @@
         <v>0.1335253012114044</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>0.9114989861620004</v>
+        <v>0.905817981234683</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>0.03481038700761003</v>
+        <v>0.03560798207754944</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>0.09266479713831061</v>
+        <v>0.09891689683749026</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>0.03466748470708781</v>
+        <v>0.03455511916979344</v>
       </c>
       <c r="M11" s="2" t="n">
-        <v>0.01602066715354348</v>
+        <v>0.01874150212072358</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>0.03819026409912341</v>
+        <v>0.03931030606062121</v>
       </c>
       <c r="O11" t="n">
         <v>7</v>
@@ -3568,126 +3626,132 @@
         <v>1</v>
       </c>
       <c r="Q11" s="2" t="n">
-        <v>8.850101383799958</v>
+        <v>1</v>
       </c>
       <c r="R11" s="2" t="n">
-        <v>3.481038700761003</v>
+        <v>9.418201876531695</v>
       </c>
       <c r="S11" s="2" t="n">
-        <v>2.426398437512705</v>
+        <v>3.560798207754943</v>
       </c>
       <c r="T11" s="2" t="n">
+        <v>2.516309506340361</v>
+      </c>
+      <c r="U11" s="2" t="n">
         <v>0.5108043375662259</v>
       </c>
-      <c r="U11" s="2" t="n">
-        <v>1.814095737319313</v>
-      </c>
       <c r="V11" s="2" t="n">
-        <v>0.7476495654105919</v>
+        <v>1.936492890972479</v>
       </c>
       <c r="W11" s="2" t="n">
+        <v>0.7695765906749886</v>
+      </c>
+      <c r="X11" s="2" t="n">
         <v>0.2</v>
       </c>
-      <c r="X11" s="2" t="n">
+      <c r="Y11" s="2" t="n">
         <v>0.001154700538379249</v>
       </c>
-      <c r="Y11" s="2" t="n">
-        <v>0.463323985691553</v>
-      </c>
       <c r="Z11" s="2" t="n">
-        <v>0.1909700563863624</v>
+        <v>0.4945844841874513</v>
       </c>
       <c r="AA11" s="2" t="n">
-        <v>2.426160385867908</v>
+        <v>0.1965722713360817</v>
       </c>
       <c r="AB11" s="2" t="n">
-        <v>0.1192923630477817</v>
+        <v>2.516044001658072</v>
       </c>
       <c r="AC11" s="2" t="n">
+        <v>0.1184745204868339</v>
+      </c>
+      <c r="AD11" s="2" t="n">
         <v>0.1257584769165896</v>
       </c>
-      <c r="AD11" s="2" t="n">
-        <v>0.0801033357677174</v>
-      </c>
       <c r="AE11" s="2" t="n">
-        <v>0.002675002278610278</v>
+        <v>0.09370751060361791</v>
       </c>
       <c r="AF11" s="2" t="n">
-        <v>1.49603129120406</v>
+        <v>0.002855484850826364</v>
       </c>
       <c r="AG11" s="2" t="n">
-        <v>0.6166250590514385</v>
+        <v>0</v>
       </c>
       <c r="AH11" s="2" t="n">
-        <v>4.969708377081383</v>
+        <v>1.401473767820903</v>
       </c>
       <c r="AI11" s="2" t="n">
-        <v>2.048384107674553</v>
+        <v>0.557014808523751</v>
       </c>
       <c r="AJ11" s="2" t="n">
-        <v>2.158316924834809</v>
+        <v>4.655595083571908</v>
       </c>
       <c r="AK11" s="2" t="n">
-        <v>0.8896019147813745</v>
+        <v>1.850363141703353</v>
       </c>
       <c r="AL11" s="2" t="n">
+        <v>2.021899254771188</v>
+      </c>
+      <c r="AM11" s="2" t="n">
+        <v>0.803602501958931</v>
+      </c>
+      <c r="AN11" s="2" t="n">
         <v>6.28</v>
       </c>
-      <c r="AM11" s="2" t="n">
+      <c r="AO11" s="2" t="n">
         <v>0.005773502691896135</v>
       </c>
-      <c r="AN11" s="2" t="n">
-        <v>0.07377770472795431</v>
-      </c>
-      <c r="AO11" s="2" t="n">
-        <v>0.03040932029135026</v>
-      </c>
       <c r="AP11" s="2" t="n">
-        <v>24.89584672782507</v>
+        <v>0.07875549111265147</v>
       </c>
       <c r="AQ11" s="2" t="n">
-        <v>10.26144388555294</v>
-      </c>
-      <c r="AR11" s="3" t="n">
-        <v>2.711893218529047e+23</v>
-      </c>
-      <c r="AS11" s="3" t="n">
-        <v>1.117774397865537e+23</v>
+        <v>0.03130140083076879</v>
+      </c>
+      <c r="AR11" s="2" t="n">
+        <v>26.57557107455335</v>
+      </c>
+      <c r="AS11" s="2" t="n">
+        <v>10.56247114656807</v>
       </c>
       <c r="AT11" s="3" t="n">
-        <v>1.703068941236241e+24</v>
+        <v>2.894864824784935e+23</v>
       </c>
       <c r="AU11" s="3" t="n">
-        <v>7.019640680016345e+23</v>
-      </c>
-      <c r="AV11" s="2" t="n">
-        <v>6.772974748003384</v>
-      </c>
-      <c r="AW11" s="2" t="n">
-        <v>2.791650393526319</v>
+        <v>1.150565159981971e+23</v>
+      </c>
+      <c r="AV11" s="3" t="n">
+        <v>1.817975109964939e+24</v>
+      </c>
+      <c r="AW11" s="3" t="n">
+        <v>7.225568534777144e+23</v>
       </c>
       <c r="AX11" s="2" t="n">
+        <v>7.229947780829852</v>
+      </c>
+      <c r="AY11" s="2" t="n">
+        <v>2.873545581089367</v>
+      </c>
+      <c r="AZ11" s="2" t="n">
         <v>0.2720523958091977</v>
       </c>
-      <c r="AY11" s="2" t="n">
+      <c r="BA11" s="2" t="n">
         <v>0.08133827031309329</v>
       </c>
-      <c r="AZ11" s="2" t="n">
+      <c r="BB11" s="2" t="n">
         <v>1.356971994134796</v>
       </c>
-      <c r="BA11" s="2" t="n">
+      <c r="BC11" s="2" t="n">
         <v>27.44711452176567</v>
       </c>
-      <c r="BB11" s="3" t="n">
+      <c r="BD11" s="3" t="n">
         <v>2.989801654609924e+23</v>
       </c>
-      <c r="BC11" s="2" t="n">
-        <v>-9.295213134034318</v>
-      </c>
-      <c r="BD11" s="2" t="n">
-        <v>37.38623918887929</v>
-      </c>
-      <c r="BE11" t="inlineStr">
+      <c r="BE11" s="2" t="n">
+        <v>-3.175355451376085</v>
+      </c>
+      <c r="BF11" s="2" t="n">
+        <v>38.48299295065057</v>
+      </c>
+      <c r="BG11" t="inlineStr">
         <is>
           <t>LAC &lt; 3σ: HVL/TVL/MFP güvenilir değil</t>
         </is>
@@ -3713,10 +3777,10 @@
         <v>1173.228</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>20.46095516938237</v>
+        <v>20.39164525436896</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>0.2342864393463963</v>
+        <v>0.2327040117564478</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>19.05540601830411</v>
@@ -3725,22 +3789,22 @@
         <v>0.2337583397087659</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>0.9313057900062501</v>
+        <v>0.9344712395985527</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.016509081049561</v>
+        <v>0.01670056033352926</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>0.07116760235128039</v>
+        <v>0.0677744288056473</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>0.01678090018163769</v>
+        <v>0.01675452909950593</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>0.005713247036504629</v>
+        <v>0.006219509151786178</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>0.01772681027726693</v>
+        <v>0.01787166862481909</v>
       </c>
       <c r="O12" t="n">
         <v>8</v>
@@ -3749,126 +3813,132 @@
         <v>1</v>
       </c>
       <c r="Q12" s="2" t="n">
-        <v>6.869420999374986</v>
+        <v>1</v>
       </c>
       <c r="R12" s="2" t="n">
-        <v>1.6509081049561</v>
+        <v>6.552876040144728</v>
       </c>
       <c r="S12" s="2" t="n">
-        <v>4.014687427582307</v>
+        <v>1.670056033352926</v>
       </c>
       <c r="T12" s="2" t="n">
+        <v>3.792283206925977</v>
+      </c>
+      <c r="U12" s="2" t="n">
         <v>0.3586335981033563</v>
       </c>
-      <c r="U12" s="2" t="n">
-        <v>1.984409791153206</v>
-      </c>
       <c r="V12" s="2" t="n">
-        <v>0.4942874948419686</v>
+        <v>1.8897958575012</v>
       </c>
       <c r="W12" s="2" t="n">
+        <v>0.4983266687598124</v>
+      </c>
+      <c r="X12" s="2" t="n">
         <v>0.2</v>
       </c>
-      <c r="X12" s="2" t="n">
+      <c r="Y12" s="2" t="n">
         <v>0.001154700538379249</v>
       </c>
-      <c r="Y12" s="2" t="n">
-        <v>0.355838011756402</v>
-      </c>
       <c r="Z12" s="2" t="n">
-        <v>0.08865785782908607</v>
+        <v>0.3388721440282365</v>
       </c>
       <c r="AA12" s="2" t="n">
-        <v>4.013609402139895</v>
+        <v>0.08937975887684815</v>
       </c>
       <c r="AB12" s="2" t="n">
-        <v>0.05725207777615897</v>
+        <v>3.791374560488032</v>
       </c>
       <c r="AC12" s="2" t="n">
+        <v>0.0570586651674392</v>
+      </c>
+      <c r="AD12" s="2" t="n">
         <v>0.0613364888379245</v>
       </c>
-      <c r="AD12" s="2" t="n">
-        <v>0.02856623518252314</v>
-      </c>
       <c r="AE12" s="2" t="n">
-        <v>0.002054431718754593</v>
+        <v>0.03109754575893089</v>
       </c>
       <c r="AF12" s="2" t="n">
-        <v>1.947928994821545</v>
+        <v>0.001956479235755674</v>
       </c>
       <c r="AG12" s="2" t="n">
-        <v>0.4853309825771756</v>
+        <v>0</v>
       </c>
       <c r="AH12" s="2" t="n">
-        <v>6.470880054743391</v>
+        <v>2.045453404108037</v>
       </c>
       <c r="AI12" s="2" t="n">
-        <v>1.612234626342409</v>
+        <v>0.5395018011211066</v>
       </c>
       <c r="AJ12" s="2" t="n">
-        <v>2.810267500832867</v>
+        <v>6.794849129889482</v>
       </c>
       <c r="AK12" s="2" t="n">
-        <v>0.7001846017538591</v>
+        <v>1.792186190386538</v>
       </c>
       <c r="AL12" s="2" t="n">
+        <v>2.950965482476114</v>
+      </c>
+      <c r="AM12" s="2" t="n">
+        <v>0.7783365730280843</v>
+      </c>
+      <c r="AN12" s="2" t="n">
         <v>6.28</v>
       </c>
-      <c r="AM12" s="2" t="n">
+      <c r="AO12" s="2" t="n">
         <v>0.005773502691896135</v>
       </c>
-      <c r="AN12" s="2" t="n">
-        <v>0.05666210378286655</v>
-      </c>
-      <c r="AO12" s="2" t="n">
-        <v>0.0141175893920553</v>
-      </c>
       <c r="AP12" s="2" t="n">
-        <v>26.00577438549107</v>
+        <v>0.05396053248857268</v>
       </c>
       <c r="AQ12" s="2" t="n">
-        <v>6.479442521295995</v>
-      </c>
-      <c r="AR12" s="3" t="n">
-        <v>2.83279713157082e+23</v>
-      </c>
-      <c r="AS12" s="3" t="n">
-        <v>7.058027158285944e+22</v>
+        <v>0.01423253213820589</v>
+      </c>
+      <c r="AR12" s="2" t="n">
+        <v>24.76585477652361</v>
+      </c>
+      <c r="AS12" s="2" t="n">
+        <v>6.532196918398787</v>
       </c>
       <c r="AT12" s="3" t="n">
-        <v>1.778996598626475e+24</v>
+        <v>2.697733254618128e+23</v>
       </c>
       <c r="AU12" s="3" t="n">
-        <v>4.432471229567854e+23</v>
-      </c>
-      <c r="AV12" s="2" t="n">
-        <v>5.201720485954501</v>
-      </c>
-      <c r="AW12" s="2" t="n">
-        <v>1.296029427964047</v>
+        <v>7.115492282213925e+22</v>
+      </c>
+      <c r="AV12" s="3" t="n">
+        <v>1.694176483900184e+24</v>
+      </c>
+      <c r="AW12" s="3" t="n">
+        <v>4.468556297667806e+23</v>
       </c>
       <c r="AX12" s="2" t="n">
+        <v>4.953709596707492</v>
+      </c>
+      <c r="AY12" s="2" t="n">
+        <v>1.306581454758791</v>
+      </c>
+      <c r="AZ12" s="2" t="n">
         <v>0.2000217493564276</v>
       </c>
-      <c r="AY12" s="2" t="n">
+      <c r="BA12" s="2" t="n">
         <v>0.05710726084448348</v>
       </c>
-      <c r="AZ12" s="2" t="n">
+      <c r="BB12" s="2" t="n">
         <v>1.932744684897548</v>
       </c>
-      <c r="BA12" s="2" t="n">
+      <c r="BC12" s="2" t="n">
         <v>26.21008473293036</v>
       </c>
-      <c r="BB12" s="3" t="n">
+      <c r="BD12" s="3" t="n">
         <v>2.855052564444956e+23</v>
       </c>
-      <c r="BC12" s="2" t="n">
-        <v>-0.7795104423397278</v>
-      </c>
-      <c r="BD12" s="2" t="n">
-        <v>24.72118113054103</v>
-      </c>
-      <c r="BE12" t="inlineStr"/>
+      <c r="BE12" s="2" t="n">
+        <v>-5.510207124940004</v>
+      </c>
+      <c r="BF12" s="2" t="n">
+        <v>24.92245631770787</v>
+      </c>
+      <c r="BG12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -3890,10 +3960,10 @@
         <v>1332.492</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>20.43446032046705</v>
+        <v>20.36980996721254</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>0.1632592034204253</v>
+        <v>0.162247758584232</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>19.04889443966352</v>
@@ -3902,22 +3972,22 @@
         <v>0.1636393570201668</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>0.9321946428203071</v>
+        <v>0.9351532719414086</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>0.01207813956309097</v>
+        <v>0.01211933096258813</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>0.07021364187366852</v>
+        <v>0.06704483591798432</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>0.01173145972647275</v>
+        <v>0.01171492634113211</v>
       </c>
       <c r="M13" s="2" t="n">
-        <v>0.005499834864907164</v>
+        <v>0.005542113380237036</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>0.01295667128760704</v>
+        <v>0.01295972684502082</v>
       </c>
       <c r="O13" t="n">
         <v>8</v>
@@ -3926,126 +3996,132 @@
         <v>1</v>
       </c>
       <c r="Q13" s="2" t="n">
-        <v>6.780535717969293</v>
+        <v>1</v>
       </c>
       <c r="R13" s="2" t="n">
-        <v>1.207813956309097</v>
+        <v>6.484672805859137</v>
       </c>
       <c r="S13" s="2" t="n">
-        <v>5.419111152478443</v>
+        <v>1.211933096258813</v>
       </c>
       <c r="T13" s="2" t="n">
+        <v>5.173321684919865</v>
+      </c>
+      <c r="U13" s="2" t="n">
         <v>0.3343771199217104</v>
       </c>
-      <c r="U13" s="2" t="n">
-        <v>2.099833920757139</v>
-      </c>
       <c r="V13" s="2" t="n">
-        <v>0.3874867781216805</v>
+        <v>2.005066492996946</v>
       </c>
       <c r="W13" s="2" t="n">
+        <v>0.3875781586986321</v>
+      </c>
+      <c r="X13" s="2" t="n">
         <v>0.2</v>
       </c>
-      <c r="X13" s="2" t="n">
+      <c r="Y13" s="2" t="n">
         <v>0.001154700538379249</v>
       </c>
-      <c r="Y13" s="2" t="n">
-        <v>0.3510682093683426</v>
-      </c>
       <c r="Z13" s="2" t="n">
-        <v>0.06481505664297314</v>
+        <v>0.3352241795899216</v>
       </c>
       <c r="AA13" s="2" t="n">
-        <v>5.416460735383826</v>
+        <v>0.0648275314902927</v>
       </c>
       <c r="AB13" s="2" t="n">
-        <v>0.0399470308635716</v>
+        <v>5.17101564541476</v>
       </c>
       <c r="AC13" s="2" t="n">
+        <v>0.039825545462964</v>
+      </c>
+      <c r="AD13" s="2" t="n">
         <v>0.04295245520376177</v>
       </c>
-      <c r="AD13" s="2" t="n">
-        <v>0.02749917432453582</v>
-      </c>
       <c r="AE13" s="2" t="n">
-        <v>0.00202689325182732</v>
+        <v>0.02771056690118518</v>
       </c>
       <c r="AF13" s="2" t="n">
-        <v>1.97439461068573</v>
+        <v>0.001935417703251122</v>
       </c>
       <c r="AG13" s="2" t="n">
-        <v>0.3645174786900434</v>
+        <v>0</v>
       </c>
       <c r="AH13" s="2" t="n">
-        <v>6.558796927631125</v>
+        <v>2.067712363135229</v>
       </c>
       <c r="AI13" s="2" t="n">
-        <v>1.210900853537961</v>
+        <v>0.3998658106882175</v>
       </c>
       <c r="AJ13" s="2" t="n">
-        <v>2.848449313594199</v>
+        <v>6.868791791244859</v>
       </c>
       <c r="AK13" s="2" t="n">
-        <v>0.525887558823474</v>
+        <v>1.328325470710101</v>
       </c>
       <c r="AL13" s="2" t="n">
+        <v>2.983078372279995</v>
+      </c>
+      <c r="AM13" s="2" t="n">
+        <v>0.5768844221009364</v>
+      </c>
+      <c r="AN13" s="2" t="n">
         <v>6.28</v>
       </c>
-      <c r="AM13" s="2" t="n">
+      <c r="AO13" s="2" t="n">
         <v>0.005773502691896135</v>
       </c>
-      <c r="AN13" s="2" t="n">
-        <v>0.05590258110960869</v>
-      </c>
-      <c r="AO13" s="2" t="n">
-        <v>0.01032099685219263</v>
-      </c>
       <c r="AP13" s="2" t="n">
-        <v>27.41444997949892</v>
+        <v>0.05337964643151618</v>
       </c>
       <c r="AQ13" s="2" t="n">
-        <v>5.061384399912215</v>
-      </c>
-      <c r="AR13" s="3" t="n">
-        <v>2.986243520932929e+23</v>
-      </c>
-      <c r="AS13" s="3" t="n">
-        <v>5.513342920427659e+22</v>
+        <v>0.01032297198118652</v>
+      </c>
+      <c r="AR13" s="2" t="n">
+        <v>26.1772107472263</v>
+      </c>
+      <c r="AS13" s="2" t="n">
+        <v>5.062352996959637</v>
       </c>
       <c r="AT13" s="3" t="n">
-        <v>1.87536093114588e+24</v>
+        <v>2.851471616189952e+23</v>
       </c>
       <c r="AU13" s="3" t="n">
-        <v>3.462422280169695e+23</v>
-      </c>
-      <c r="AV13" s="2" t="n">
-        <v>5.131994436526965</v>
-      </c>
-      <c r="AW13" s="2" t="n">
-        <v>0.947492895203022</v>
+        <v>5.514398008769545e+22</v>
+      </c>
+      <c r="AV13" s="3" t="n">
+        <v>1.79072417496729e+24</v>
+      </c>
+      <c r="AW13" s="3" t="n">
+        <v>3.46308108102112e+23</v>
       </c>
       <c r="AX13" s="2" t="n">
+        <v>4.90038282799846</v>
+      </c>
+      <c r="AY13" s="2" t="n">
+        <v>0.9476742169024295</v>
+      </c>
+      <c r="AZ13" s="2" t="n">
         <v>0.1872003428981714</v>
       </c>
-      <c r="AY13" s="2" t="n">
+      <c r="BA13" s="2" t="n">
         <v>0.0532447643187437</v>
       </c>
-      <c r="AZ13" s="2" t="n">
+      <c r="BB13" s="2" t="n">
         <v>2.072950388238991</v>
       </c>
-      <c r="BA13" s="2" t="n">
+      <c r="BC13" s="2" t="n">
         <v>26.11106498328598</v>
       </c>
-      <c r="BB13" s="3" t="n">
+      <c r="BD13" s="3" t="n">
         <v>2.844266388321013e+23</v>
       </c>
-      <c r="BC13" s="2" t="n">
-        <v>4.991696037856935</v>
-      </c>
-      <c r="BD13" s="2" t="n">
-        <v>19.38405960519829</v>
-      </c>
-      <c r="BE13" t="inlineStr"/>
+      <c r="BE13" s="2" t="n">
+        <v>0.2533246498473077</v>
+      </c>
+      <c r="BF13" s="2" t="n">
+        <v>19.38776913235868</v>
+      </c>
+      <c r="BG13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4058,11 +4134,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U25"/>
+  <dimension ref="A1:U22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
@@ -4070,9 +4146,9 @@
     <col width="20" customWidth="1" min="7" max="7"/>
     <col width="21" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="21" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
     <col width="22" customWidth="1" min="11" max="11"/>
-    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="21" customWidth="1" min="12" max="12"/>
     <col width="20" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="15" customWidth="1" min="15" max="15"/>
@@ -4081,7 +4157,7 @@
     <col width="14" customWidth="1" min="18" max="18"/>
     <col width="19" customWidth="1" min="19" max="19"/>
     <col width="10" customWidth="1" min="20" max="20"/>
-    <col width="30" customWidth="1" min="21" max="21"/>
+    <col width="21" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4199,55 +4275,55 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Am-241 59.5</t>
+          <t>Ba-133 81</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Am-241</t>
+          <t>Ba-133</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>59.5409</v>
+        <v>80.89906428571429</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>58.27177208762703</v>
+        <v>81.86215190008812</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>11.68636613438182</v>
+        <v>11.15875332473758</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>20.05493520397539</v>
+        <v>13.63115074027949</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>191.3316718921741</v>
+        <v>30422.10813646906</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>2371.467042506279</v>
+        <v>732.7803266095203</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>0.08068072145331848</v>
+        <v>41.51600013230188</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>0.02657384331835751</v>
+        <v>4.225292796731814</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>0.3293704225703165</v>
+        <v>0.1017750453624334</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>0.9318980502176999</v>
+        <v>0.8359216186033491</v>
       </c>
       <c r="N2" t="n">
-        <v>55</v>
+        <v>144</v>
       </c>
       <c r="O2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="P2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>568.0944328786358</v>
+        <v>0.4319682991690021</v>
       </c>
       <c r="R2" s="2" t="n">
         <v>7200</v>
@@ -4257,7 +4333,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>hayir</t>
+          <t>evet</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -4274,55 +4350,55 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Ba-133 81</t>
+          <t>Co-57 122</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ba-133</t>
+          <t>Co-57</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>80.89906428571429</v>
+        <v>123.6601720398837</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>81.81541368459227</v>
+        <v>118.0621475082746</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>11.16476958194304</v>
+        <v>17.6816067295944</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>13.64629118051581</v>
+        <v>14.97652473952768</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>30423.02568108368</v>
+        <v>-476.1070846554946</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>772.6377722878862</v>
+        <v>944.8394735791286</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>39.3755350466454</v>
+        <v>0.5039026183484506</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>4.225420233483845</v>
+        <v>-0.06612598397992982</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>0.1073108017066509</v>
+        <v>0.1312277046637678</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>0.7341551471873931</v>
+        <v>1.045657949692261</v>
       </c>
       <c r="N3" t="n">
-        <v>102</v>
+        <v>182</v>
       </c>
       <c r="O3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>1.228810574341478</v>
+        <v>129.1742627876981</v>
       </c>
       <c r="R3" s="2" t="n">
         <v>7200</v>
@@ -4332,12 +4408,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>evet</t>
+          <t>hayir</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>ok; at bound: mu[0]</t>
         </is>
       </c>
     </row>
@@ -4349,55 +4425,55 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Co-57 122</t>
+          <t>Ba-133 303</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Co-57</t>
+          <t>Ba-133</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>123.6601720398837</v>
+        <v>295.4176231113203</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>118.0621475956089</v>
+        <v>304.1434940065175</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>17.81435122072853</v>
+        <v>28.34311932953135</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>15.08896084268003</v>
+        <v>9.318995766164241</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>-505.7019184417441</v>
+        <v>19132.25211382071</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>952.9958877180524</v>
+        <v>1065.077047688722</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.5306443867797235</v>
+        <v>17.96325641918468</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>-0.07023637756135336</v>
+        <v>2.657257238030654</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>0.1323605399608406</v>
+        <v>0.1479273677345447</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>1.043282617633975</v>
+        <v>0.9794496525507638</v>
       </c>
       <c r="N4" t="n">
-        <v>182</v>
+        <v>385</v>
       </c>
       <c r="O4" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="P4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>196.2692110805026</v>
+        <v>4.547770046620847</v>
       </c>
       <c r="R4" s="2" t="n">
         <v>7200</v>
@@ -4407,12 +4483,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>hayir</t>
+          <t>evet</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>ok; at bound: mu[0]</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -4424,7 +4500,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Ba-133 303</t>
+          <t>Ba-133 356</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -4433,34 +4509,34 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>295.4176231113203</v>
+        <v>359.5183270178899</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>304.1496177072581</v>
+        <v>357.7568783486643</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>28.26982244781574</v>
+        <v>30.33303194131847</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>9.294709183236668</v>
+        <v>8.478671907394153</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>18993.63311251814</v>
+        <v>48970.15028034492</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>1059.583506376555</v>
+        <v>1221.846560328737</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>17.92556509063683</v>
+        <v>40.07880520379707</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>2.638004598960852</v>
+        <v>6.801409761159016</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0.1471643758856326</v>
+        <v>0.169700911156769</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0.9613164097427928</v>
+        <v>0.9794496525507638</v>
       </c>
       <c r="N5" t="n">
         <v>385</v>
@@ -4472,7 +4548,7 @@
         <v>0</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>3.86545051303146</v>
+        <v>0.9563207648367428</v>
       </c>
       <c r="R5" s="2" t="n">
         <v>7200</v>
@@ -4499,46 +4575,46 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Ba-133 356</t>
+          <t>Cs-137 662</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ba-133</t>
+          <t>Cs-137</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>359.5183270178899</v>
+        <v>661.657</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>357.7645743711666</v>
+        <v>663.7713627561997</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>30.15261924335883</v>
+        <v>47.77633351043883</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>8.428061748807103</v>
+        <v>7.197709360653282</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>48802.52526381952</v>
+        <v>42197.61065057106</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>1209.862906968657</v>
+        <v>999.8683375033045</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>40.33723571714049</v>
+        <v>42.20316722493636</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>6.778128508863822</v>
+        <v>5.860779257023759</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>0.1680365148567579</v>
+        <v>0.1388706024310145</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.9613164097427928</v>
+        <v>1.116512968168842</v>
       </c>
       <c r="N6" t="n">
-        <v>385</v>
+        <v>480</v>
       </c>
       <c r="O6" t="n">
         <v>7</v>
@@ -4547,7 +4623,7 @@
         <v>0</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>0.8762395118381023</v>
+        <v>0.808199015743882</v>
       </c>
       <c r="R6" s="2" t="n">
         <v>7200</v>
@@ -4574,55 +4650,55 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Cs-137 662</t>
+          <t>Co-60 1173</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Cs-137</t>
+          <t>Co-60</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>661.657</v>
+        <v>1173.228</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>663.8371398844827</v>
+        <v>1174.103984595093</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>47.50121010415928</v>
+        <v>68.68199453841559</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>7.155551753616133</v>
+        <v>5.849736943197716</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>41934.6099915837</v>
+        <v>146819.8458314565</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>1000.495743876628</v>
+        <v>1675.468884646424</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>41.91383146628828</v>
+        <v>87.62910918661439</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>5.824251387719959</v>
+        <v>20.39164525436896</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>0.1389577422050872</v>
+        <v>0.2327040117564478</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>1.137246698427965</v>
+        <v>0.995295709527133</v>
       </c>
       <c r="N7" t="n">
-        <v>480</v>
+        <v>813</v>
       </c>
       <c r="O7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>0.7576599252205672</v>
+        <v>1.518350484712985</v>
       </c>
       <c r="R7" s="2" t="n">
         <v>7200</v>
@@ -4649,7 +4725,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Co-60 1173</t>
+          <t>Co-60 1332</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -4658,34 +4734,34 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>1173.228</v>
+        <v>1332.492</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1174.122260563667</v>
+        <v>1333.124696427111</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>68.7794587881242</v>
+        <v>74.09873758127297</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>5.857946919012069</v>
+        <v>5.558275064580527</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>147318.877219553</v>
+        <v>146662.6317639303</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>1686.862363294053</v>
+        <v>1168.18386180647</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>87.33307495928314</v>
+        <v>125.5475585299837</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>20.46095516938237</v>
+        <v>20.36980996721254</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>0.2342864393463963</v>
+        <v>0.162247758584232</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0.9964753804604803</v>
+        <v>0.995295709527133</v>
       </c>
       <c r="N8" t="n">
         <v>813</v>
@@ -4697,7 +4773,7 @@
         <v>0</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>1.528187322030101</v>
+        <v>0.6055814102326043</v>
       </c>
       <c r="R8" s="2" t="n">
         <v>7200</v>
@@ -4719,60 +4795,60 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bos (I0)</t>
+          <t>ORNEK-A</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Co-60 1332</t>
+          <t>Ba-133 81</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Co-60</t>
+          <t>Ba-133</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>1332.492</v>
+        <v>80.89906428571429</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1333.075475165222</v>
+        <v>81.85058791935174</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>74.2035043624882</v>
+        <v>10.89853229032159</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>5.566339321732058</v>
+        <v>13.31515456072231</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>147128.1143073628</v>
+        <v>10149.61362293075</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>1175.466264627062</v>
+        <v>567.6320331994332</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>125.1657480396018</v>
+        <v>17.88062165153523</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>20.43446032046705</v>
+        <v>1.409668558740381</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>0.1632592034204253</v>
+        <v>0.07883778238881016</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0.9964753804604803</v>
+        <v>0.8197115446249397</v>
       </c>
       <c r="N9" t="n">
-        <v>813</v>
+        <v>144</v>
       </c>
       <c r="O9" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>0.6284202106248489</v>
+        <v>2.543551109507598</v>
       </c>
       <c r="R9" s="2" t="n">
         <v>7200</v>
@@ -4799,55 +4875,55 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Am-241 59.5</t>
+          <t>Co-57 122</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Am-241</t>
+          <t>Co-57</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>59.5409</v>
+        <v>123.6601720398837</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>57.0411902751751</v>
+        <v>123.9311835616332</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>5.846195405294923</v>
+        <v>9.11228848785793</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>10.2490768111465</v>
+        <v>7.352700285740617</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>218.0758492856029</v>
+        <v>-738.7372480690207</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>273.9006325010076</v>
+        <v>301.4458178668475</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.7961860010849032</v>
+        <v>2.45064686349482</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>0.03028831240077819</v>
+        <v>-0.1026023955651418</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>0.03804175451402884</v>
+        <v>0.04186747470372882</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>0.9249024980814543</v>
+        <v>0.9407177623505466</v>
       </c>
       <c r="N10" t="n">
-        <v>55</v>
+        <v>182</v>
       </c>
       <c r="O10" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>329.6975537164268</v>
+        <v>14.85219789307338</v>
       </c>
       <c r="R10" s="2" t="n">
         <v>7200</v>
@@ -4862,7 +4938,7 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>ok; at bound: mu[1]</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -4874,7 +4950,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Ba-133 81</t>
+          <t>Ba-133 303</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -4883,46 +4959,46 @@
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>80.89906428571429</v>
+        <v>295.4176231113203</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>81.88334620475658</v>
+        <v>303.9113531202871</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>11.42190348642081</v>
+        <v>27.63782061797948</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>13.94899453407696</v>
+        <v>9.094040197649518</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>10759.70474085268</v>
+        <v>16525.18289693273</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>641.8534871221793</v>
+        <v>1061.233037931164</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>16.76349035524447</v>
+        <v>15.57168153108763</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>1.494403436229539</v>
+        <v>2.295164291240656</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>0.08914631765585825</v>
+        <v>0.1473934774904395</v>
       </c>
       <c r="M11" s="2" t="n">
-        <v>0.8725961529591204</v>
+        <v>1.038514744985847</v>
       </c>
       <c r="N11" t="n">
-        <v>102</v>
+        <v>385</v>
       </c>
       <c r="O11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" s="2" t="n">
-        <v>4.022735556448853</v>
+        <v>6.077292507243214</v>
       </c>
       <c r="R11" s="2" t="n">
         <v>7200</v>
@@ -4949,55 +5025,55 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Co-57 122</t>
+          <t>Ba-133 356</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Co-57</t>
+          <t>Ba-133</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>123.6601720398837</v>
+        <v>359.5183270178899</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>123.9314184251704</v>
+        <v>357.7185747356816</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>9.112628176522172</v>
+        <v>30.79456827445374</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>7.352960445639026</v>
+        <v>8.608601970755322</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>-738.7612333680777</v>
+        <v>43170.38904351014</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>301.4532843773235</v>
+        <v>1266.482995433416</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>2.450665730493033</v>
+        <v>34.08682880004746</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>-0.1026057268566775</v>
+        <v>5.995887367154187</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>0.04186851171907271</v>
+        <v>0.1759004160324189</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>0.9407177332464175</v>
+        <v>1.038514744985847</v>
       </c>
       <c r="N12" t="n">
-        <v>182</v>
+        <v>385</v>
       </c>
       <c r="O12" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="P12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q12" s="2" t="n">
-        <v>13.48778800655237</v>
+        <v>1.249995493301876</v>
       </c>
       <c r="R12" s="2" t="n">
         <v>7200</v>
@@ -5007,7 +5083,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>hayir</t>
+          <t>evet</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -5024,46 +5100,46 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Ba-133 303</t>
+          <t>Cs-137 662</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ba-133</t>
+          <t>Cs-137</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>295.4176231113203</v>
+        <v>661.657</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>303.9114210663175</v>
+        <v>663.6112916008173</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>27.63779284436715</v>
+        <v>45.94314507994105</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>9.094029025758863</v>
+        <v>6.923201226596559</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>16525.2872024454</v>
+        <v>37721.33594772279</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>1061.233847633265</v>
+        <v>890.0476583459963</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>15.57176793719842</v>
+        <v>42.38125407556438</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>2.295178778117416</v>
+        <v>5.23907443718372</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>0.1473935899490647</v>
+        <v>0.1236177303258328</v>
       </c>
       <c r="M13" s="2" t="n">
-        <v>1.038514751421322</v>
+        <v>0.8758496406522237</v>
       </c>
       <c r="N13" t="n">
-        <v>385</v>
+        <v>480</v>
       </c>
       <c r="O13" t="n">
         <v>7</v>
@@ -5072,7 +5148,7 @@
         <v>0</v>
       </c>
       <c r="Q13" s="2" t="n">
-        <v>6.077269667540452</v>
+        <v>0.7159135315139149</v>
       </c>
       <c r="R13" s="2" t="n">
         <v>7200</v>
@@ -5099,55 +5175,55 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Ba-133 356</t>
+          <t>Co-60 1173</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ba-133</t>
+          <t>Co-60</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>359.5183270178899</v>
+        <v>1173.228</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>357.7185760153048</v>
+        <v>1174.486569585544</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>30.79468667748418</v>
+        <v>68.95835886537941</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>8.608635039452535</v>
+        <v>5.871362061612476</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>43170.62867609593</v>
+        <v>137193.1085307276</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>1266.49126491073</v>
+        <v>1757.379507224589</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>34.08679544200319</v>
+        <v>78.06686487848899</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>5.995920649457767</v>
+        <v>19.0545984070455</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>0.1759015645709348</v>
+        <v>0.2440804871145263</v>
       </c>
       <c r="M14" s="2" t="n">
-        <v>1.038514751421322</v>
+        <v>1.064079088852244</v>
       </c>
       <c r="N14" t="n">
-        <v>385</v>
+        <v>814</v>
       </c>
       <c r="O14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
       </c>
       <c r="Q14" s="2" t="n">
-        <v>1.249975785142871</v>
+        <v>1.749277616552799</v>
       </c>
       <c r="R14" s="2" t="n">
         <v>7200</v>
@@ -5174,55 +5250,55 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Cs-137 662</t>
+          <t>Co-60 1332</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Cs-137</t>
+          <t>Co-60</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>661.657</v>
+        <v>1332.492</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>663.6112912944417</v>
+        <v>1332.990484984475</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>45.94309191315408</v>
+        <v>74.3804889351529</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>6.923193218056519</v>
+        <v>5.57997148314372</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>37721.26467800869</v>
+        <v>137400.5558292752</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>890.0461897943704</v>
+        <v>1222.570906948947</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>42.38124392928813</v>
+        <v>112.3865741024156</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>5.239064538612317</v>
+        <v>19.08341053184378</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>0.1236175263603292</v>
+        <v>0.1698015148540204</v>
       </c>
       <c r="M15" s="2" t="n">
-        <v>0.8758496459644954</v>
+        <v>1.064079088852244</v>
       </c>
       <c r="N15" t="n">
-        <v>480</v>
+        <v>814</v>
       </c>
       <c r="O15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P15" t="n">
         <v>0</v>
       </c>
       <c r="Q15" s="2" t="n">
-        <v>0.7154153917255712</v>
+        <v>0.8239698632955774</v>
       </c>
       <c r="R15" s="2" t="n">
         <v>7200</v>
@@ -5244,60 +5320,60 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ORNEK-A</t>
+          <t>ORNEK-B</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Co-60 1173</t>
+          <t>Ba-133 81</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Co-60</t>
+          <t>Ba-133</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>1173.228</v>
+        <v>80.89906428571429</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>1174.486573568287</v>
+        <v>84.80675395097072</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>68.95839605238186</v>
+        <v>8.161337456913039</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>5.871365207937175</v>
+        <v>9.623452233098496</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>137193.2793790714</v>
+        <v>2815.302814085828</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>1757.383708160068</v>
+        <v>331.9296791896713</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>78.06677548109799</v>
+        <v>8.481624243299761</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>19.05462213598214</v>
+        <v>0.3910142797341428</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>0.2440810705777872</v>
+        <v>0.04610134433189879</v>
       </c>
       <c r="M16" s="2" t="n">
-        <v>1.064079081470766</v>
+        <v>1.066216691920698</v>
       </c>
       <c r="N16" t="n">
-        <v>814</v>
+        <v>147</v>
       </c>
       <c r="O16" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
       </c>
       <c r="Q16" s="2" t="n">
-        <v>1.749532283949103</v>
+        <v>5.025908613179402</v>
       </c>
       <c r="R16" s="2" t="n">
         <v>7200</v>
@@ -5312,67 +5388,67 @@
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>ok; at bound: mu[0]</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ORNEK-A</t>
+          <t>ORNEK-B</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Co-60 1332</t>
+          <t>Co-57 122</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Co-60</t>
+          <t>Co-57</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>1332.492</v>
+        <v>123.6601720398837</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>1332.990474847087</v>
+        <v>118.0623477664169</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>74.38052896673479</v>
+        <v>13.80611662535883</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>5.579974528720266</v>
+        <v>11.6939201079364</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>137400.649437694</v>
+        <v>-852.5129731766549</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>1222.573478097213</v>
+        <v>674.8592971999615</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>112.3864143131433</v>
+        <v>1.263245504231461</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>19.08342353301305</v>
+        <v>-0.1184045796078687</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>0.1698018719579462</v>
+        <v>0.0937304579444391</v>
       </c>
       <c r="M17" s="2" t="n">
-        <v>1.064079081470766</v>
+        <v>1.046543877739239</v>
       </c>
       <c r="N17" t="n">
-        <v>814</v>
+        <v>184</v>
       </c>
       <c r="O17" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q17" s="2" t="n">
-        <v>0.8239937690813449</v>
+        <v>64.39669927312882</v>
       </c>
       <c r="R17" s="2" t="n">
         <v>7200</v>
@@ -5382,12 +5458,12 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>evet</t>
+          <t>hayir</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>ok; at bound: mu[0]</t>
         </is>
       </c>
     </row>
@@ -5399,55 +5475,55 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Am-241 59.5</t>
+          <t>Ba-133 303</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Am-241</t>
+          <t>Ba-133</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>59.5409</v>
+        <v>295.4176231113203</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>57.04127578718745</v>
+        <v>304.9006495066023</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>5.090132147320905</v>
+        <v>26.91763210044309</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>8.923594497274982</v>
+        <v>8.828328881555963</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>304.9436045455369</v>
+        <v>14122.87638488289</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>402.2698417778074</v>
+        <v>1006.328386900786</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>0.7580573358367034</v>
+        <v>14.0340634018856</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>0.04235327840910235</v>
+        <v>1.961510609011513</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>0.05587081135802881</v>
+        <v>0.139767831513998</v>
       </c>
       <c r="M18" s="2" t="n">
-        <v>1.452263796055479</v>
+        <v>0.9638989559676633</v>
       </c>
       <c r="N18" t="n">
-        <v>57</v>
+        <v>389</v>
       </c>
       <c r="O18" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P18" t="n">
         <v>0</v>
       </c>
       <c r="Q18" s="2" t="n">
-        <v>64.90228967225497</v>
+        <v>6.793825617842744</v>
       </c>
       <c r="R18" s="2" t="n">
         <v>7200</v>
@@ -5457,12 +5533,12 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>hayir</t>
+          <t>evet</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>ok; at bound: mu[1],sigma[1]</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -5474,7 +5550,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Ba-133 81</t>
+          <t>Ba-133 356</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -5483,46 +5559,46 @@
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>80.89906428571429</v>
+        <v>359.5183270178899</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>85.0401788095963</v>
+        <v>358.2551555487144</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>8.064450649048814</v>
+        <v>29.58198836165808</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>9.483106411505789</v>
+        <v>8.257240099266518</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>2734.586910491206</v>
+        <v>40362.25251317619</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>316.337641908431</v>
+        <v>1172.335056141209</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>8.64451948871382</v>
+        <v>34.42893932220221</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>0.3798037375682231</v>
+        <v>5.605868404607805</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>0.0439357835983932</v>
+        <v>0.1628243133529456</v>
       </c>
       <c r="M19" s="2" t="n">
-        <v>0.9769227812208684</v>
+        <v>0.9638989559676633</v>
       </c>
       <c r="N19" t="n">
-        <v>104</v>
+        <v>389</v>
       </c>
       <c r="O19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P19" t="n">
         <v>0</v>
       </c>
       <c r="Q19" s="2" t="n">
-        <v>4.982511179158569</v>
+        <v>1.387993241691263</v>
       </c>
       <c r="R19" s="2" t="n">
         <v>7200</v>
@@ -5549,51 +5625,55 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Co-57 122</t>
+          <t>Cs-137 662</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Co-57</t>
+          <t>Cs-137</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>123.6601720398837</v>
+        <v>661.657</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>118.0623477664169</v>
+        <v>662.3450264600644</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>18.70607432564658</v>
+        <v>47.34811091637879</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>15.8442337286533</v>
+        <v>7.148556873663429</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>-1049.999999999839</v>
-      </c>
-      <c r="I20" t="inlineStr"/>
+        <v>38223.35449242744</v>
+      </c>
+      <c r="I20" s="2" t="n">
+        <v>961.3821687221119</v>
+      </c>
       <c r="J20" s="2" t="n">
+        <v>39.75875123961855</v>
+      </c>
+      <c r="K20" s="2" t="n">
+        <v>5.308799235059366</v>
+      </c>
+      <c r="L20" s="2" t="n">
+        <v>0.1335253012114044</v>
+      </c>
+      <c r="M20" s="2" t="n">
+        <v>1.067169704700461</v>
+      </c>
+      <c r="N20" t="n">
+        <v>481</v>
+      </c>
+      <c r="O20" t="n">
+        <v>7</v>
+      </c>
+      <c r="P20" t="n">
         <v>0</v>
       </c>
-      <c r="K20" s="2" t="n">
-        <v>-0.1458333333333109</v>
-      </c>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" s="2" t="n">
-        <v>1.027160349840322</v>
-      </c>
-      <c r="N20" t="n">
-        <v>184</v>
-      </c>
-      <c r="O20" t="n">
-        <v>3</v>
-      </c>
-      <c r="P20" t="n">
-        <v>2</v>
-      </c>
       <c r="Q20" s="2" t="n">
-        <v>55.09342486538264</v>
+        <v>1.539840875896927</v>
       </c>
       <c r="R20" s="2" t="n">
         <v>7200</v>
@@ -5603,12 +5683,12 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>hayir</t>
+          <t>evet</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>ok; at bound: A[0],mu[0]</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -5620,55 +5700,55 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Ba-133 303</t>
+          <t>Co-60 1173</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Ba-133</t>
+          <t>Co-60</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>295.4176231113203</v>
+        <v>1173.228</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>304.9006495066023</v>
+        <v>1173.684680609335</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>26.91763210044309</v>
+        <v>69.39201646329387</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>8.828328881555963</v>
+        <v>5.912321904659098</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>14122.87638488289</v>
+        <v>137198.9233317896</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>1006.328386900786</v>
+        <v>1683.060045903115</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>14.0340634018856</v>
+        <v>81.51754517954227</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>1.961510609011513</v>
+        <v>19.05540601830411</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>0.139767831513998</v>
+        <v>0.2337583397087659</v>
       </c>
       <c r="M21" s="2" t="n">
-        <v>0.9638989559676633</v>
+        <v>0.9650036123401272</v>
       </c>
       <c r="N21" t="n">
-        <v>389</v>
+        <v>807</v>
       </c>
       <c r="O21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P21" t="n">
         <v>0</v>
       </c>
       <c r="Q21" s="2" t="n">
-        <v>6.793825617842744</v>
+        <v>1.372437330713494</v>
       </c>
       <c r="R21" s="2" t="n">
         <v>7200</v>
@@ -5695,55 +5775,55 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Ba-133 356</t>
+          <t>Co-60 1332</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Ba-133</t>
+          <t>Co-60</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>359.5183270178899</v>
+        <v>1332.492</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>358.2551555487144</v>
+        <v>1333.511883383879</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>29.58198836165808</v>
+        <v>75.06471008696295</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>8.257240099266518</v>
+        <v>5.629099449528791</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>40362.25251317619</v>
+        <v>137152.0399655773</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>1172.335056141209</v>
+        <v>1178.203370545201</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>34.42893932220221</v>
+        <v>116.4077810285941</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>5.605868404607805</v>
+        <v>19.04889443966352</v>
       </c>
       <c r="L22" s="2" t="n">
-        <v>0.1628243133529456</v>
+        <v>0.1636393570201668</v>
       </c>
       <c r="M22" s="2" t="n">
-        <v>0.9638989559676633</v>
+        <v>0.9650036123401272</v>
       </c>
       <c r="N22" t="n">
-        <v>389</v>
+        <v>807</v>
       </c>
       <c r="O22" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P22" t="n">
         <v>0</v>
       </c>
       <c r="Q22" s="2" t="n">
-        <v>1.387993241691263</v>
+        <v>0.550852226079654</v>
       </c>
       <c r="R22" s="2" t="n">
         <v>7200</v>
@@ -5757,231 +5837,6 @@
         </is>
       </c>
       <c r="U22" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>ORNEK-B</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Cs-137 662</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Cs-137</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="n">
-        <v>661.657</v>
-      </c>
-      <c r="E23" s="2" t="n">
-        <v>662.3450264600644</v>
-      </c>
-      <c r="F23" s="2" t="n">
-        <v>47.34811091637879</v>
-      </c>
-      <c r="G23" s="2" t="n">
-        <v>7.148556873663429</v>
-      </c>
-      <c r="H23" s="2" t="n">
-        <v>38223.35449242744</v>
-      </c>
-      <c r="I23" s="2" t="n">
-        <v>961.3821687221119</v>
-      </c>
-      <c r="J23" s="2" t="n">
-        <v>39.75875123961855</v>
-      </c>
-      <c r="K23" s="2" t="n">
-        <v>5.308799235059366</v>
-      </c>
-      <c r="L23" s="2" t="n">
-        <v>0.1335253012114044</v>
-      </c>
-      <c r="M23" s="2" t="n">
-        <v>1.067169704700461</v>
-      </c>
-      <c r="N23" t="n">
-        <v>481</v>
-      </c>
-      <c r="O23" t="n">
-        <v>7</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" s="2" t="n">
-        <v>1.539840875896927</v>
-      </c>
-      <c r="R23" s="2" t="n">
-        <v>7200</v>
-      </c>
-      <c r="S23" s="2" t="n">
-        <v>7379.999999999999</v>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>evet</t>
-        </is>
-      </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>ORNEK-B</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Co-60 1173</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Co-60</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="n">
-        <v>1173.228</v>
-      </c>
-      <c r="E24" s="2" t="n">
-        <v>1173.684680609335</v>
-      </c>
-      <c r="F24" s="2" t="n">
-        <v>69.39201646329387</v>
-      </c>
-      <c r="G24" s="2" t="n">
-        <v>5.912321904659098</v>
-      </c>
-      <c r="H24" s="2" t="n">
-        <v>137198.9233317896</v>
-      </c>
-      <c r="I24" s="2" t="n">
-        <v>1683.060045903115</v>
-      </c>
-      <c r="J24" s="2" t="n">
-        <v>81.51754517954227</v>
-      </c>
-      <c r="K24" s="2" t="n">
-        <v>19.05540601830411</v>
-      </c>
-      <c r="L24" s="2" t="n">
-        <v>0.2337583397087659</v>
-      </c>
-      <c r="M24" s="2" t="n">
-        <v>0.9650036123401272</v>
-      </c>
-      <c r="N24" t="n">
-        <v>807</v>
-      </c>
-      <c r="O24" t="n">
-        <v>8</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" s="2" t="n">
-        <v>1.372437330713494</v>
-      </c>
-      <c r="R24" s="2" t="n">
-        <v>7200</v>
-      </c>
-      <c r="S24" s="2" t="n">
-        <v>7379.999999999999</v>
-      </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>evet</t>
-        </is>
-      </c>
-      <c r="U24" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>ORNEK-B</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Co-60 1332</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Co-60</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="n">
-        <v>1332.492</v>
-      </c>
-      <c r="E25" s="2" t="n">
-        <v>1333.511883383879</v>
-      </c>
-      <c r="F25" s="2" t="n">
-        <v>75.06471008696295</v>
-      </c>
-      <c r="G25" s="2" t="n">
-        <v>5.629099449528791</v>
-      </c>
-      <c r="H25" s="2" t="n">
-        <v>137152.0399655773</v>
-      </c>
-      <c r="I25" s="2" t="n">
-        <v>1178.203370545201</v>
-      </c>
-      <c r="J25" s="2" t="n">
-        <v>116.4077810285941</v>
-      </c>
-      <c r="K25" s="2" t="n">
-        <v>19.04889443966352</v>
-      </c>
-      <c r="L25" s="2" t="n">
-        <v>0.1636393570201668</v>
-      </c>
-      <c r="M25" s="2" t="n">
-        <v>0.9650036123401272</v>
-      </c>
-      <c r="N25" t="n">
-        <v>807</v>
-      </c>
-      <c r="O25" t="n">
-        <v>8</v>
-      </c>
-      <c r="P25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" s="2" t="n">
-        <v>0.550852226079654</v>
-      </c>
-      <c r="R25" s="2" t="n">
-        <v>7200</v>
-      </c>
-      <c r="S25" s="2" t="n">
-        <v>7379.999999999999</v>
-      </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>evet</t>
-        </is>
-      </c>
-      <c r="U25" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -6005,11 +5860,11 @@
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
     <col width="22" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="23" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
     <col width="22" customWidth="1" min="10" max="10"/>
     <col width="20" customWidth="1" min="11" max="11"/>
     <col width="22" customWidth="1" min="12" max="12"/>
@@ -6097,25 +5952,25 @@
         <v>80.89906428571429</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.3536697780701941</v>
+        <v>0.3336262423827134</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.02575188751468622</v>
+        <v>0.02222761952383706</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>1.039391631515506</v>
+        <v>1.097733947374646</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0.06483452065304618</v>
+        <v>0.06089300504698356</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>0.03314017824988575</v>
+        <v>0.0270340738587338</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>0.07281336747290618</v>
+        <v>0.06662431397809242</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>14.27473646102501</v>
+        <v>16.47647655682587</v>
       </c>
       <c r="L2" t="n">
         <v>6</v>
@@ -6141,25 +5996,25 @@
         <v>295.4176231113203</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.8700435090300904</v>
+        <v>0.863734326655423</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.09018530043733011</v>
+        <v>0.08622567476627345</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.1392120582045707</v>
+        <v>0.1464900497604954</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.08506560731668297</v>
+        <v>0.08498915868226771</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>0.05923196415926527</v>
+        <v>0.05237039653365842</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>0.1036560809905555</v>
+        <v>0.09982893131057902</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>1.343018729574148</v>
+        <v>1.467410777991286</v>
       </c>
       <c r="L3" t="n">
         <v>7</v>
@@ -6185,25 +6040,25 @@
         <v>359.5183270178899</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.8845982547567292</v>
+        <v>0.8815653780184004</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.03657660951493821</v>
+        <v>0.03645592105708186</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.122621686467866</v>
+        <v>0.1260561131123555</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.03840892230736111</v>
+        <v>0.038512271395664</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>0.01531124780969072</v>
+        <v>0.01506409543499459</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.04134827230130252</v>
+        <v>0.0413536215986932</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>2.965581864565676</v>
+        <v>3.048248454165353</v>
       </c>
       <c r="L4" t="n">
         <v>7</v>
@@ -6229,25 +6084,25 @@
         <v>661.657</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.8995258256981372</v>
+        <v>0.8939211335941434</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.03082949172978986</v>
+        <v>0.0310279302504868</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.1058875148329042</v>
+        <v>0.112137725156227</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.03355543086765616</v>
+        <v>0.03343932473995194</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>0.006976737994220559</v>
+        <v>0.009305377291983722</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.03427304792040026</v>
+        <v>0.03470991912422338</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>3.08952723080917</v>
+        <v>3.230711219893575</v>
       </c>
       <c r="L5" t="n">
         <v>7</v>
@@ -6273,25 +6128,25 @@
         <v>1173.228</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.9312674788758323</v>
+        <v>0.9344316345912793</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.02904294055376019</v>
+        <v>0.029429833718739</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.07120874020186956</v>
+        <v>0.06781681196833199</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.01718128345025596</v>
+        <v>0.01715551688639427</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>0.02602689172215715</v>
+        <v>0.02641244322607389</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.03118646491212064</v>
+        <v>0.03149490302906068</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>2.283321960425025</v>
+        <v>2.153263082148775</v>
       </c>
       <c r="L6" t="n">
         <v>8</v>
@@ -6317,25 +6172,25 @@
         <v>1332.492</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.9338843910597039</v>
+        <v>0.9368477449009412</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.01417664979245994</v>
+        <v>0.01425876183993261</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.06840262672312966</v>
+        <v>0.06523450204843681</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.01195837565675302</v>
+        <v>0.01194214700467852</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>0.009350877410202204</v>
+        <v>0.009435653034942549</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.01518030489445627</v>
+        <v>0.01521993506152942</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>4.506011387696815</v>
+        <v>4.286122232763424</v>
       </c>
       <c r="L7" t="n">
         <v>8</v>
@@ -6361,25 +6216,25 @@
         <v>80.89906428571429</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.08988543543160819</v>
+        <v>0.09254134530903636</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.01166213367276159</v>
+        <v>0.01203434246183361</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>2.409219359176548</v>
+        <v>2.380099758014007</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.1184352006467461</v>
+        <v>0.1203372639903481</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>0.05297846476803805</v>
+        <v>0.0492959617440567</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.1297444198469177</v>
+        <v>0.1300428735031422</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>18.56896321259232</v>
+        <v>18.30242360767657</v>
       </c>
       <c r="L8" t="n">
         <v>6</v>
@@ -6405,25 +6260,25 @@
         <v>295.4176231113203</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.7435584493613772</v>
+        <v>0.7381711416337046</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.08859439141877606</v>
+        <v>0.09265339807660357</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>0.2963079023703815</v>
+        <v>0.3035795820334734</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>0.09049535306375088</v>
+        <v>0.09042324205229151</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>0.07750562547833741</v>
+        <v>0.08705332111633689</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.1191491959977961</v>
+        <v>0.1255175024473932</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>2.486864471799392</v>
+        <v>2.418623507591775</v>
       </c>
       <c r="L9" t="n">
         <v>7</v>
@@ -6449,25 +6304,25 @@
         <v>359.5183270178899</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.827052540723735</v>
+        <v>0.8242215366322112</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0.0332282114597998</v>
+        <v>0.03359411841006289</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.1898870542670253</v>
+        <v>0.1933159300715522</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>0.0381867062304185</v>
+        <v>0.03829067709600099</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>0.0124875834798939</v>
+        <v>0.0139673822696891</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.04017666329967687</v>
+        <v>0.04075860301749607</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>4.72630225289397</v>
+        <v>4.7429478873103</v>
       </c>
       <c r="L10" t="n">
         <v>7</v>
@@ -6493,25 +6348,25 @@
         <v>661.657</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0.9114989861620004</v>
+        <v>0.905817981234683</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>0.03481038700761003</v>
+        <v>0.03560798207754944</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>0.09266479713831061</v>
+        <v>0.09891689683749026</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>0.03466748470708781</v>
+        <v>0.03455511916979344</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>0.01602066715354348</v>
+        <v>0.01874150212072358</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>0.03819026409912341</v>
+        <v>0.03931030606062121</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>2.426398437512705</v>
+        <v>2.516309506340361</v>
       </c>
       <c r="L11" t="n">
         <v>7</v>
@@ -6537,25 +6392,25 @@
         <v>1173.228</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>0.9313057900062501</v>
+        <v>0.9344712395985527</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>0.016509081049561</v>
+        <v>0.01670056033352926</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>0.07116760235128039</v>
+        <v>0.0677744288056473</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>0.01678090018163769</v>
+        <v>0.01675452909950593</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>0.005713247036504629</v>
+        <v>0.006219509151786178</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.01772681027726693</v>
+        <v>0.01787166862481909</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>4.014687427582307</v>
+        <v>3.792283206925977</v>
       </c>
       <c r="L12" t="n">
         <v>8</v>
@@ -6581,25 +6436,25 @@
         <v>1332.492</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.9321946428203071</v>
+        <v>0.9351532719414086</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>0.01207813956309097</v>
+        <v>0.01211933096258813</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0.07021364187366852</v>
+        <v>0.06704483591798432</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>0.01173145972647275</v>
+        <v>0.01171492634113211</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>0.005499834864907164</v>
+        <v>0.005542113380237036</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>0.01295667128760704</v>
+        <v>0.01295972684502082</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>5.419111152478443</v>
+        <v>5.173321684919864</v>
       </c>
       <c r="L13" t="n">
         <v>8</v>
@@ -7895,11 +7750,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>E[keV] = -0.390149 + 0.501217*ch^1 + 1.31125e-05*ch^2</t>
+          <t>E[keV] = -0.471082 + 0.501416*ch^1 + 1.30397e-05*ch^2</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>0.2120731801585374</v>
+        <v>0.2202653076469119</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -7907,13 +7762,13 @@
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>7.066249904828322</v>
+        <v>7.075152709122584</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.6775724129381016</v>
+        <v>0.6798837911218731</v>
       </c>
       <c r="G2" t="n">
-        <v>2773269</v>
+        <v>2788065</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>7200</v>
@@ -7925,7 +7780,7 @@
         <v>2.439024390243894</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>385.17625</v>
+        <v>387.23125</v>
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
@@ -7938,11 +7793,11 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>E[keV] = -0.212649 + 0.50142*ch^1 + 1.30318e-05*ch^2</t>
+          <t>E[keV] = -0.212672 + 0.50142*ch^1 + 1.30318e-05*ch^2</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>0.1602247777681179</v>
+        <v>0.1602150787387269</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -7950,13 +7805,13 @@
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>7.026943101208025</v>
+        <v>6.996551697591823</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.6793588013093762</v>
+        <v>0.7084943505160866</v>
       </c>
       <c r="G3" t="n">
-        <v>2719537</v>
+        <v>2734556</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>7200</v>
@@ -7968,7 +7823,7 @@
         <v>2.439024390243894</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>377.7134722222222</v>
+        <v>379.7994444444444</v>
       </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
@@ -7999,7 +7854,7 @@
         <v>0.7047960905009037</v>
       </c>
       <c r="G4" t="n">
-        <v>2707852</v>
+        <v>2722886</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>7200</v>
@@ -8011,7 +7866,7 @@
         <v>2.439024390243894</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>376.0905555555556</v>
+        <v>378.1786111111111</v>
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
@@ -8127,34 +7982,34 @@
         <v>80.89906428571429</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>5.196958157577531</v>
+        <v>5.488669736873228</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.3653011650747898</v>
+        <v>0.3346254077456884</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.1269824014855127</v>
+        <v>0.1204354943652124</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.2982672399388321</v>
+        <v>0.2796323359132595</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0.1657008912494287</v>
+        <v>0.135170369293669</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>0.03000465191244601</v>
+        <v>0.03168884950076702</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>12.08328329378732</v>
+        <v>12.95362059287131</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>66.66670584691771</v>
+        <v>69.83239779419587</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>20.57536622439344</v>
+        <v>16.31718260929316</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>0.6746446349015484</v>
+        <v>0.8967990036396524</v>
       </c>
     </row>
     <row r="3">
@@ -8172,34 +8027,34 @@
         <v>295.4176231113203</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.6960602910228537</v>
+        <v>0.7324502488024771</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.5182959850853944</v>
+        <v>0.4991625696546232</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.2789312345088457</v>
+        <v>0.2783459681987293</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.3210939194679245</v>
+        <v>0.3210957011943698</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.2961598207963263</v>
+        <v>0.2618519826682921</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>0.004018705963942527</v>
+        <v>0.004228803483141174</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>28.96267084514298</v>
+        <v>31.09466243515352</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>38.38030958972762</v>
+        <v>41.37947336089958</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>32.65100759556228</v>
+        <v>27.518687071125</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>0.006011969567111563</v>
+        <v>0.007177132821888221</v>
       </c>
     </row>
     <row r="4">
@@ -8217,34 +8072,34 @@
         <v>359.5183270178899</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.61310843233933</v>
+        <v>0.6302805655617775</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.206771663006709</v>
+        <v>0.2068001263770772</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.1239549490962107</v>
+        <v>0.1247542179607265</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.1466843666342067</v>
+        <v>0.1466842230859867</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.07655623904845361</v>
+        <v>0.07532047717497292</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>0.003539783184535407</v>
+        <v>0.003638926541920808</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>35.93732120419731</v>
+        <v>36.3922474290921</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>50.3252126361697</v>
+        <v>50.31126188520831</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>13.70815916516535</v>
+        <v>13.26552754703414</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0.0293069944676399</v>
+        <v>0.03096313866543964</v>
       </c>
     </row>
     <row r="5">
@@ -8262,34 +8117,34 @@
         <v>661.657</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.5294375741645209</v>
+        <v>0.5606886257811352</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.1713924992972248</v>
+        <v>0.1735797833795434</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.1192923630477817</v>
+        <v>0.1184745204868339</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.1179767165008737</v>
+        <v>0.1179766882566798</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.03488368997110279</v>
+        <v>0.04652688645991861</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>0.003056709259629878</v>
+        <v>0.003237137290262989</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>48.44418561053381</v>
+        <v>46.58559375308499</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>47.38151969261709</v>
+        <v>46.19490917856986</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>4.142487555310852</v>
+        <v>7.184717518769808</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0.031807141538242</v>
+        <v>0.03477954957534325</v>
       </c>
     </row>
     <row r="6">
@@ -8307,34 +8162,34 @@
         <v>1173.228</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.3560437010093477</v>
+        <v>0.3390840598416599</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.1559458733453403</v>
+        <v>0.1574866836282875</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.05725207777615897</v>
+        <v>0.0570586651674392</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.06404773310011544</v>
+        <v>0.0640476597565753</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.1301344586107858</v>
+        <v>0.1320622161303694</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>0.00205561926621017</v>
+        <v>0.00195770273227493</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>13.47828798030932</v>
+        <v>13.1266993900307</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>16.86785084706013</v>
+        <v>16.53936592855004</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>69.63648566165584</v>
+        <v>70.31848192999377</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.01737551097470845</v>
+        <v>0.01545275142550042</v>
       </c>
     </row>
     <row r="7">
@@ -8352,34 +8207,34 @@
         <v>1332.492</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0.3420131336156483</v>
+        <v>0.326172510242184</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.07592720537902414</v>
+        <v>0.07612297199582552</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.0399470308635716</v>
+        <v>0.039825545462964</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.04448936315441521</v>
+        <v>0.04448929990021409</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.04675438705101102</v>
+        <v>0.04717826517471274</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>0.001974613747593815</v>
+        <v>0.001883157865905804</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>27.68051587351529</v>
+        <v>27.37108378806642</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>34.33345804978492</v>
+        <v>34.1569962305277</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>37.91839139008139</v>
+        <v>38.41072131113231</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0.06763468661840991</v>
+        <v>0.06119867027356249</v>
       </c>
     </row>
     <row r="8">
@@ -8397,34 +8252,34 @@
         <v>80.89906428571429</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>12.04609679588274</v>
+        <v>11.90049879007003</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.6524395070062234</v>
+        <v>0.6538344230554637</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.1269824014855127</v>
+        <v>0.1204354943652124</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.5784011484418468</v>
+        <v>0.5895097279214951</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.2648923238401902</v>
+        <v>0.2464798087202835</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>0.0695481722778717</v>
+        <v>0.06870756179937731</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>3.787970346732461</v>
+        <v>3.392918566078202</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>78.59190058335221</v>
+        <v>81.29173430759921</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>16.48383447536555</v>
+        <v>14.21108160789864</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>1.136294594549792</v>
+        <v>1.104265518423946</v>
       </c>
     </row>
     <row r="9">
@@ -8442,34 +8297,34 @@
         <v>295.4176231113203</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>1.481539511851907</v>
+        <v>1.517897910167367</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.5958073832908334</v>
+        <v>0.6276486963139815</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.2789312345088457</v>
+        <v>0.2783459681987293</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>0.3562760019545162</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>0.387528127391687</v>
+        <v>0.4352666055816844</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>0.008553672359827631</v>
+        <v>0.008763587670374972</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>21.91707210746003</v>
+        <v>19.66693162102406</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>35.75702505414081</v>
+        <v>32.22106403861891</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>42.30529210429482</v>
+        <v>48.09250900953912</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0.02061073410432759</v>
+        <v>0.01949533081791522</v>
       </c>
     </row>
     <row r="10">
@@ -8487,34 +8342,34 @@
         <v>359.5183270178899</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>0.9494352713351265</v>
+        <v>0.9665796503577609</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.2009580912160673</v>
+        <v>0.2038694080511562</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0.1239549490962107</v>
+        <v>0.1247542179607265</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>0.1452266639180385</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>0.06243791739946949</v>
+        <v>0.06983691134844548</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>0.005481567094834592</v>
+        <v>0.005580550213272662</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>38.04667851570621</v>
+        <v>37.44607927536492</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>52.22539437299538</v>
+        <v>50.7444556745</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>9.653522736010988</v>
+        <v>11.73453605357386</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>0.07440437528740122</v>
+        <v>0.07492899656120731</v>
       </c>
     </row>
     <row r="11">
@@ -8532,34 +8387,34 @@
         <v>661.657</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>0.463323985691553</v>
+        <v>0.4945844841874513</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0.1909700563863624</v>
+        <v>0.1965722713360817</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>0.1192923630477817</v>
+        <v>0.1184745204868339</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>0.1257584769165896</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>0.0801033357677174</v>
+        <v>0.09370751060361791</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>0.002675002278610278</v>
+        <v>0.002855484850826364</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>39.02067074814754</v>
+        <v>36.32498198163337</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>43.36546275827427</v>
+        <v>40.92889560629868</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>17.59424564618501</v>
+        <v>22.72502082067368</v>
       </c>
       <c r="M11" s="2" t="n">
-        <v>0.01962084739318229</v>
+        <v>0.02110159139426511</v>
       </c>
     </row>
     <row r="12">
@@ -8577,34 +8432,34 @@
         <v>1173.228</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>0.355838011756402</v>
+        <v>0.3388721440282365</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>0.08865785782908607</v>
+        <v>0.08937975887684815</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>0.05725207777615897</v>
+        <v>0.0570586651674392</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>0.0613364888379245</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>0.02856623518252314</v>
+        <v>0.03109754575893089</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>0.002054431718754593</v>
+        <v>0.001956479235755674</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>41.70115060350606</v>
+        <v>40.75349482101784</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>47.86337907642142</v>
+        <v>47.09333702460098</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>10.38177345196271</v>
+        <v>12.1052530841881</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>0.05369686810981892</v>
+        <v>0.04791507019305245</v>
       </c>
     </row>
     <row r="13">
@@ -8622,34 +8477,34 @@
         <v>1332.492</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>0.3510682093683426</v>
+        <v>0.3352241795899216</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.06481505664297314</v>
+        <v>0.0648275314902927</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>0.0399470308635716</v>
+        <v>0.039825545462964</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>0.04295245520376177</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>0.02749917432453582</v>
+        <v>0.02771056690118518</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>0.00202689325182732</v>
+        <v>0.001935417703251122</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>37.98544341555788</v>
+        <v>37.74022594386586</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>43.91614166155483</v>
+        <v>43.89924160572907</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>18.00062143322743</v>
+        <v>18.27140110772132</v>
       </c>
       <c r="M13" s="2" t="n">
-        <v>0.09779348965984844</v>
+        <v>0.08913134268374699</v>
       </c>
     </row>
   </sheetData>
